--- a/artfynd/A 379-2026 artfynd.xlsx
+++ b/artfynd/A 379-2026 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>131143977</v>
       </c>
       <c r="B3" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131143975</v>
       </c>
       <c r="B4" t="n">
-        <v>80379</v>
+        <v>80380</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>131143973</v>
       </c>
       <c r="B5" t="n">
-        <v>80379</v>
+        <v>80380</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131143999</v>
+        <v>131144271</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503460</v>
+        <v>503292</v>
       </c>
       <c r="R6" t="n">
-        <v>7036014</v>
+        <v>7036126</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,6 +1287,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1304,17 +1309,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1332,10 +1342,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131143978</v>
+        <v>131144288</v>
       </c>
       <c r="B7" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,10 +1380,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503218</v>
+        <v>503258</v>
       </c>
       <c r="R7" t="n">
-        <v>7036101</v>
+        <v>7035950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1463,10 +1473,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131144288</v>
+        <v>131143999</v>
       </c>
       <c r="B8" t="n">
-        <v>80350</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,21 +1484,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1501,10 +1511,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503258</v>
+        <v>503460</v>
       </c>
       <c r="R8" t="n">
-        <v>7035950</v>
+        <v>7036014</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1539,11 +1549,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1561,22 +1566,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1594,10 +1594,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131144278</v>
+        <v>131143978</v>
       </c>
       <c r="B9" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503277</v>
+        <v>503218</v>
       </c>
       <c r="R9" t="n">
-        <v>7035964</v>
+        <v>7036101</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131144271</v>
+        <v>131144278</v>
       </c>
       <c r="B10" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503292</v>
+        <v>503277</v>
       </c>
       <c r="R10" t="n">
-        <v>7036126</v>
+        <v>7035964</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131143990</v>
+        <v>131144272</v>
       </c>
       <c r="B11" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503447</v>
+        <v>503267</v>
       </c>
       <c r="R11" t="n">
-        <v>7036031</v>
+        <v>7036125</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131144287</v>
+        <v>131143987</v>
       </c>
       <c r="B12" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503222</v>
+        <v>503418</v>
       </c>
       <c r="R12" t="n">
-        <v>7035916</v>
+        <v>7036017</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131144272</v>
+        <v>131143990</v>
       </c>
       <c r="B13" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503267</v>
+        <v>503447</v>
       </c>
       <c r="R13" t="n">
-        <v>7036125</v>
+        <v>7036031</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131143987</v>
+        <v>131144287</v>
       </c>
       <c r="B14" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503418</v>
+        <v>503222</v>
       </c>
       <c r="R14" t="n">
-        <v>7036017</v>
+        <v>7035916</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2383,7 +2383,7 @@
         <v>131144279</v>
       </c>
       <c r="B15" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>131144296</v>
       </c>
       <c r="B16" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>131143980</v>
       </c>
       <c r="B17" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>131144292</v>
       </c>
       <c r="B18" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131143984</v>
       </c>
       <c r="B19" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>131144274</v>
       </c>
       <c r="B20" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>131143986</v>
       </c>
       <c r="B21" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3310,41 +3310,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131143972</v>
+        <v>131143976</v>
       </c>
       <c r="B22" t="n">
-        <v>80379</v>
+        <v>80351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3352,10 +3348,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503377</v>
+        <v>503419</v>
       </c>
       <c r="R22" t="n">
-        <v>7036016</v>
+        <v>7036154</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3388,11 +3384,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3445,10 +3436,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131143976</v>
+        <v>131143989</v>
       </c>
       <c r="B23" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3483,10 +3474,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503419</v>
+        <v>503448</v>
       </c>
       <c r="R23" t="n">
-        <v>7036154</v>
+        <v>7036030</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3521,6 +3512,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lunglav på en gran vid en rönn med lunglav.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3538,22 +3534,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3571,10 +3567,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131143989</v>
+        <v>131143998</v>
       </c>
       <c r="B24" t="n">
-        <v>80350</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3582,21 +3578,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3609,10 +3605,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503448</v>
+        <v>503444</v>
       </c>
       <c r="R24" t="n">
-        <v>7036030</v>
+        <v>7036006</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3649,7 +3645,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Lunglav på en gran vid en rönn med lunglav.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3677,14 +3673,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3702,37 +3693,41 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131143998</v>
+        <v>131143972</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>80380</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3740,10 +3735,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503444</v>
+        <v>503377</v>
       </c>
       <c r="R25" t="n">
-        <v>7036006</v>
+        <v>7036016</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3780,7 +3775,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3800,17 +3795,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
         <v>131144299</v>
       </c>
       <c r="B26" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>131144290</v>
       </c>
       <c r="B27" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>131144284</v>
       </c>
       <c r="B28" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>131143988</v>
       </c>
       <c r="B29" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>131143993</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>131144281</v>
       </c>
       <c r="B31" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>131143994</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>131144293</v>
       </c>
       <c r="B33" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131144264</v>
+        <v>131143996</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4872,29 +4872,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4904,10 +4903,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503447</v>
+        <v>503386</v>
       </c>
       <c r="R34" t="n">
-        <v>7035991</v>
+        <v>7036016</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4944,7 +4943,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4953,6 +4952,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4961,6 +4961,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
+        </is>
+      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4971,9 +4976,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4991,10 +5001,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131143967</v>
+        <v>131144294</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5002,31 +5012,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5034,10 +5039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503201</v>
+        <v>503563</v>
       </c>
       <c r="R35" t="n">
-        <v>7036058</v>
+        <v>7036044</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5074,7 +5079,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5083,6 +5088,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5091,29 +5097,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5131,10 +5132,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131144269</v>
+        <v>131144259</v>
       </c>
       <c r="B36" t="n">
-        <v>80351</v>
+        <v>91814</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5142,26 +5143,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5169,10 +5174,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503190</v>
+        <v>503326</v>
       </c>
       <c r="R36" t="n">
-        <v>7035938</v>
+        <v>7035948</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5207,11 +5212,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5229,22 +5229,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5262,10 +5262,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131144259</v>
+        <v>131144269</v>
       </c>
       <c r="B37" t="n">
-        <v>91813</v>
+        <v>80352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5273,30 +5273,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5304,10 +5300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503326</v>
+        <v>503190</v>
       </c>
       <c r="R37" t="n">
-        <v>7035948</v>
+        <v>7035938</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5342,6 +5338,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5359,22 +5360,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5392,10 +5393,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131143996</v>
+        <v>131144264</v>
       </c>
       <c r="B38" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5403,28 +5404,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5434,10 +5436,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503386</v>
+        <v>503447</v>
       </c>
       <c r="R38" t="n">
-        <v>7036016</v>
+        <v>7035991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5474,7 +5476,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5483,7 +5485,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5492,11 +5493,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
-        </is>
-      </c>
       <c r="AJ38" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5507,14 +5503,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5532,10 +5523,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131144294</v>
+        <v>131143967</v>
       </c>
       <c r="B39" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5543,26 +5534,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5570,10 +5566,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503563</v>
+        <v>503201</v>
       </c>
       <c r="R39" t="n">
-        <v>7036044</v>
+        <v>7036058</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5610,7 +5606,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5619,7 +5615,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5628,24 +5623,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5666,7 +5666,7 @@
         <v>131143992</v>
       </c>
       <c r="B40" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>131144270</v>
       </c>
       <c r="B41" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>131144282</v>
       </c>
       <c r="B42" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>131144276</v>
       </c>
       <c r="B43" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>131144295</v>
       </c>
       <c r="B46" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>131143981</v>
       </c>
       <c r="B47" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>131144285</v>
       </c>
       <c r="B48" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>131143979</v>
       </c>
       <c r="B49" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>131144301</v>
       </c>
       <c r="B50" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7077,32 +7077,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131143983</v>
+        <v>131144300</v>
       </c>
       <c r="B51" t="n">
-        <v>80350</v>
+        <v>80311</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503376</v>
+        <v>503318</v>
       </c>
       <c r="R51" t="n">
-        <v>7035991</v>
+        <v>7035950</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7151,6 +7151,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7203,32 +7208,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131144300</v>
+        <v>131143983</v>
       </c>
       <c r="B52" t="n">
-        <v>80310</v>
+        <v>80351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7241,10 +7246,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503318</v>
+        <v>503376</v>
       </c>
       <c r="R52" t="n">
-        <v>7035950</v>
+        <v>7035991</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7277,11 +7282,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7337,7 +7337,7 @@
         <v>131144000</v>
       </c>
       <c r="B53" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>131144286</v>
       </c>
       <c r="B54" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>131144277</v>
       </c>
       <c r="B55" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>131143982</v>
       </c>
       <c r="B56" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>131143997</v>
       </c>
       <c r="B57" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>131144280</v>
       </c>
       <c r="B58" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>131144275</v>
       </c>
       <c r="B59" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>131144291</v>
       </c>
       <c r="B60" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>131143991</v>
       </c>
       <c r="B61" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>131144297</v>
       </c>
       <c r="B62" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>131143995</v>
       </c>
       <c r="B63" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8995,41 +8995,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131144268</v>
+        <v>131144283</v>
       </c>
       <c r="B66" t="n">
-        <v>80379</v>
+        <v>80351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9037,10 +9033,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503554</v>
+        <v>503196</v>
       </c>
       <c r="R66" t="n">
-        <v>7036090</v>
+        <v>7035909</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9130,41 +9126,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131143968</v>
+        <v>131144001</v>
       </c>
       <c r="B67" t="n">
-        <v>80379</v>
+        <v>79246</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9172,10 +9164,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503216</v>
+        <v>503574</v>
       </c>
       <c r="R67" t="n">
-        <v>7036102</v>
+        <v>7036113</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9210,11 +9202,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -9232,22 +9219,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9265,10 +9247,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131144283</v>
+        <v>131144298</v>
       </c>
       <c r="B68" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9303,10 +9285,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503196</v>
+        <v>503191</v>
       </c>
       <c r="R68" t="n">
-        <v>7035909</v>
+        <v>7035913</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9396,37 +9378,41 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131144001</v>
+        <v>131144268</v>
       </c>
       <c r="B69" t="n">
-        <v>79245</v>
+        <v>80380</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9434,10 +9420,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503574</v>
+        <v>503554</v>
       </c>
       <c r="R69" t="n">
-        <v>7036113</v>
+        <v>7036090</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9472,6 +9458,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9489,17 +9480,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9517,10 +9513,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131143974</v>
+        <v>131143968</v>
       </c>
       <c r="B70" t="n">
-        <v>80379</v>
+        <v>80380</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9547,7 +9543,11 @@
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503424</v>
+        <v>503216</v>
       </c>
       <c r="R70" t="n">
-        <v>7036001</v>
+        <v>7036102</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9648,32 +9648,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131144298</v>
+        <v>131143974</v>
       </c>
       <c r="B71" t="n">
-        <v>80350</v>
+        <v>80380</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503191</v>
+        <v>503424</v>
       </c>
       <c r="R71" t="n">
-        <v>7035913</v>
+        <v>7036001</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9909,10 +9909,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131144261</v>
+        <v>131144289</v>
       </c>
       <c r="B73" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9920,31 +9920,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9952,10 +9947,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503332</v>
+        <v>503258</v>
       </c>
       <c r="R73" t="n">
-        <v>7035950</v>
+        <v>7035952</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9992,7 +9987,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10001,6 +9996,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -10011,22 +10007,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10044,10 +10040,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131144289</v>
+        <v>131144261</v>
       </c>
       <c r="B74" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10055,26 +10051,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10082,10 +10083,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503258</v>
+        <v>503332</v>
       </c>
       <c r="R74" t="n">
-        <v>7035952</v>
+        <v>7035950</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10122,7 +10123,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10131,7 +10132,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10175,41 +10175,37 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131143970</v>
+        <v>131144302</v>
       </c>
       <c r="B75" t="n">
-        <v>80379</v>
+        <v>79246</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10217,10 +10213,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503376</v>
+        <v>503606</v>
       </c>
       <c r="R75" t="n">
-        <v>7035991</v>
+        <v>7036064</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10272,22 +10268,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10305,10 +10296,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131144302</v>
+        <v>131144273</v>
       </c>
       <c r="B76" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10316,21 +10307,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10343,10 +10334,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503606</v>
+        <v>503267</v>
       </c>
       <c r="R76" t="n">
-        <v>7036064</v>
+        <v>7036145</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10381,6 +10372,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -10398,17 +10394,22 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10426,37 +10427,41 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131144273</v>
+        <v>131143970</v>
       </c>
       <c r="B77" t="n">
-        <v>80350</v>
+        <v>80380</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10464,10 +10469,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503267</v>
+        <v>503376</v>
       </c>
       <c r="R77" t="n">
-        <v>7036145</v>
+        <v>7035991</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10500,11 +10505,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 379-2026 artfynd.xlsx
+++ b/artfynd/A 379-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131144266</v>
+        <v>131143977</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>80353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503547</v>
+        <v>503254</v>
       </c>
       <c r="R2" t="n">
-        <v>7036037</v>
+        <v>7036092</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,22 +777,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,39 +810,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131143977</v>
+        <v>131143975</v>
       </c>
       <c r="B3" t="n">
-        <v>80351</v>
+        <v>80382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503254</v>
+        <v>503441</v>
       </c>
       <c r="R3" t="n">
-        <v>7036092</v>
+        <v>7036004</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131143975</v>
+        <v>131143973</v>
       </c>
       <c r="B4" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,11 +975,7 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -987,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503441</v>
+        <v>503418</v>
       </c>
       <c r="R4" t="n">
-        <v>7036004</v>
+        <v>7036017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1080,37 +1076,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131143973</v>
+        <v>131144266</v>
       </c>
       <c r="B5" t="n">
-        <v>80380</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1118,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503418</v>
+        <v>503547</v>
       </c>
       <c r="R5" t="n">
-        <v>7036017</v>
+        <v>7036037</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1158,7 +1159,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,7 +1168,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1178,22 +1178,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131144271</v>
+        <v>131143999</v>
       </c>
       <c r="B6" t="n">
-        <v>80351</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503292</v>
+        <v>503460</v>
       </c>
       <c r="R6" t="n">
-        <v>7036126</v>
+        <v>7036014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,11 +1287,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1309,22 +1304,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1342,10 +1332,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131144288</v>
+        <v>131143978</v>
       </c>
       <c r="B7" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503258</v>
+        <v>503218</v>
       </c>
       <c r="R7" t="n">
-        <v>7035950</v>
+        <v>7036101</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1473,10 +1463,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131143999</v>
+        <v>131144271</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>80353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,21 +1474,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1511,10 +1501,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503460</v>
+        <v>503292</v>
       </c>
       <c r="R8" t="n">
-        <v>7036014</v>
+        <v>7036126</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1549,6 +1539,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1566,17 +1561,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1594,10 +1594,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131143978</v>
+        <v>131144288</v>
       </c>
       <c r="B9" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503218</v>
+        <v>503258</v>
       </c>
       <c r="R9" t="n">
-        <v>7036101</v>
+        <v>7035950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1728,7 +1728,7 @@
         <v>131144278</v>
       </c>
       <c r="B10" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131144272</v>
+        <v>131143990</v>
       </c>
       <c r="B11" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503267</v>
+        <v>503447</v>
       </c>
       <c r="R11" t="n">
-        <v>7036125</v>
+        <v>7036031</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131143987</v>
+        <v>131144287</v>
       </c>
       <c r="B12" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503418</v>
+        <v>503222</v>
       </c>
       <c r="R12" t="n">
-        <v>7036017</v>
+        <v>7035916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131143990</v>
+        <v>131144272</v>
       </c>
       <c r="B13" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503447</v>
+        <v>503267</v>
       </c>
       <c r="R13" t="n">
-        <v>7036031</v>
+        <v>7036125</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131144287</v>
+        <v>131143987</v>
       </c>
       <c r="B14" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503222</v>
+        <v>503418</v>
       </c>
       <c r="R14" t="n">
-        <v>7035916</v>
+        <v>7036017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2380,10 +2380,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131144279</v>
+        <v>131143984</v>
       </c>
       <c r="B15" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503274</v>
+        <v>503375</v>
       </c>
       <c r="R15" t="n">
-        <v>7035964</v>
+        <v>7036013</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Växer här på en rönn i äldre granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2511,10 +2511,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131144296</v>
+        <v>131144279</v>
       </c>
       <c r="B16" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503556</v>
+        <v>503274</v>
       </c>
       <c r="R16" t="n">
-        <v>7036089</v>
+        <v>7035964</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131143980</v>
+        <v>131144296</v>
       </c>
       <c r="B17" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2672,11 +2672,7 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2684,10 +2680,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503337</v>
+        <v>503556</v>
       </c>
       <c r="R17" t="n">
-        <v>7036003</v>
+        <v>7036089</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2724,7 +2720,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med lunglavsbålar på en rönn.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2740,11 +2736,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2782,10 +2773,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131144292</v>
+        <v>131143980</v>
       </c>
       <c r="B18" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2812,7 +2803,11 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2820,10 +2815,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503355</v>
+        <v>503337</v>
       </c>
       <c r="R18" t="n">
-        <v>7035956</v>
+        <v>7036003</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2860,7 +2855,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Rikligt med lunglavsbålar på en rönn.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2876,6 +2871,11 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2913,10 +2913,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131143984</v>
+        <v>131144292</v>
       </c>
       <c r="B19" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503375</v>
+        <v>503355</v>
       </c>
       <c r="R19" t="n">
-        <v>7036013</v>
+        <v>7035956</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Växer här på en rönn i äldre granskog.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3047,7 +3047,7 @@
         <v>131144274</v>
       </c>
       <c r="B20" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>131143986</v>
       </c>
       <c r="B21" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3310,37 +3310,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131143976</v>
+        <v>131143972</v>
       </c>
       <c r="B22" t="n">
-        <v>80351</v>
+        <v>80382</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3348,10 +3352,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503419</v>
+        <v>503377</v>
       </c>
       <c r="R22" t="n">
-        <v>7036154</v>
+        <v>7036016</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3384,6 +3388,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3436,10 +3445,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131143989</v>
+        <v>131143976</v>
       </c>
       <c r="B23" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3474,10 +3483,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503448</v>
+        <v>503419</v>
       </c>
       <c r="R23" t="n">
-        <v>7036030</v>
+        <v>7036154</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3512,11 +3521,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Lunglav på en gran vid en rönn med lunglav.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3534,22 +3538,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3567,10 +3571,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131143998</v>
+        <v>131143989</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>80353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3578,21 +3582,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3605,10 +3609,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503444</v>
+        <v>503448</v>
       </c>
       <c r="R24" t="n">
-        <v>7036006</v>
+        <v>7036030</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3645,7 +3649,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Lunglav på en gran vid en rönn med lunglav.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3673,9 +3677,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3693,41 +3702,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131143972</v>
+        <v>131143998</v>
       </c>
       <c r="B25" t="n">
-        <v>80380</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3735,10 +3740,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503377</v>
+        <v>503444</v>
       </c>
       <c r="R25" t="n">
-        <v>7036016</v>
+        <v>7036006</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3775,7 +3780,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3795,22 +3800,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
         <v>131144299</v>
       </c>
       <c r="B26" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>131144290</v>
       </c>
       <c r="B27" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>131144284</v>
       </c>
       <c r="B28" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>131143988</v>
       </c>
       <c r="B29" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131143993</v>
+        <v>131144293</v>
       </c>
       <c r="B30" t="n">
-        <v>79246</v>
+        <v>80353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4358,21 +4358,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503307</v>
+        <v>503484</v>
       </c>
       <c r="R30" t="n">
-        <v>7036124</v>
+        <v>7036019</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4445,17 +4445,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4473,10 +4478,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131144281</v>
+        <v>131143993</v>
       </c>
       <c r="B31" t="n">
-        <v>80351</v>
+        <v>79248</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4484,21 +4489,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4511,10 +4516,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503194</v>
+        <v>503307</v>
       </c>
       <c r="R31" t="n">
-        <v>7035963</v>
+        <v>7036124</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4551,7 +4556,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4571,22 +4576,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131143994</v>
+        <v>131144281</v>
       </c>
       <c r="B32" t="n">
-        <v>79246</v>
+        <v>80353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4615,21 +4615,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503252</v>
+        <v>503194</v>
       </c>
       <c r="R32" t="n">
-        <v>7036082</v>
+        <v>7035963</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4702,17 +4702,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4730,10 +4735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131144293</v>
+        <v>131143994</v>
       </c>
       <c r="B33" t="n">
-        <v>80351</v>
+        <v>79248</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4741,21 +4746,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4768,10 +4773,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503484</v>
+        <v>503252</v>
       </c>
       <c r="R33" t="n">
-        <v>7036019</v>
+        <v>7036082</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4808,7 +4813,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4828,22 +4833,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4864,7 +4864,7 @@
         <v>131143996</v>
       </c>
       <c r="B34" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131144294</v>
+        <v>131144264</v>
       </c>
       <c r="B35" t="n">
-        <v>80351</v>
+        <v>57886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5012,26 +5012,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5039,10 +5044,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503563</v>
+        <v>503447</v>
       </c>
       <c r="R35" t="n">
-        <v>7036044</v>
+        <v>7035991</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5079,7 +5084,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5088,7 +5093,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5099,22 +5103,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5132,10 +5131,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131144259</v>
+        <v>131143967</v>
       </c>
       <c r="B36" t="n">
-        <v>91814</v>
+        <v>57886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5143,28 +5142,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5174,10 +5174,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503326</v>
+        <v>503201</v>
       </c>
       <c r="R36" t="n">
-        <v>7035948</v>
+        <v>7036058</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5212,13 +5212,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5227,6 +5231,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ36" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5239,12 +5248,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5262,10 +5271,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131144269</v>
+        <v>131144294</v>
       </c>
       <c r="B37" t="n">
-        <v>80352</v>
+        <v>80353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5273,21 +5282,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5300,10 +5309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503190</v>
+        <v>503563</v>
       </c>
       <c r="R37" t="n">
-        <v>7035938</v>
+        <v>7036044</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5393,10 +5402,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131144264</v>
+        <v>131144269</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>80354</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5404,31 +5413,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5436,10 +5440,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503447</v>
+        <v>503190</v>
       </c>
       <c r="R38" t="n">
-        <v>7035991</v>
+        <v>7035938</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5476,7 +5480,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5485,6 +5489,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5495,17 +5500,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5523,10 +5533,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131143967</v>
+        <v>131144259</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>91816</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5534,29 +5544,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5566,10 +5575,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503201</v>
+        <v>503326</v>
       </c>
       <c r="R39" t="n">
-        <v>7036058</v>
+        <v>7035948</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5604,17 +5613,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5623,11 +5628,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ39" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5666,7 +5666,7 @@
         <v>131143992</v>
       </c>
       <c r="B40" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5784,10 +5784,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131144270</v>
+        <v>131144267</v>
       </c>
       <c r="B41" t="n">
-        <v>80351</v>
+        <v>57886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5795,26 +5795,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5822,10 +5827,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503423</v>
+        <v>503564</v>
       </c>
       <c r="R41" t="n">
-        <v>7036145</v>
+        <v>7036045</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5862,7 +5867,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5871,7 +5876,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5882,22 +5886,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5915,10 +5914,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131144282</v>
+        <v>131144263</v>
       </c>
       <c r="B42" t="n">
-        <v>80351</v>
+        <v>57886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5926,26 +5925,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5953,10 +5957,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503179</v>
+        <v>503363</v>
       </c>
       <c r="R42" t="n">
-        <v>7035940</v>
+        <v>7035960</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5993,7 +5997,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6002,7 +6006,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6013,22 +6016,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6046,10 +6049,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131144276</v>
+        <v>131144270</v>
       </c>
       <c r="B43" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6084,10 +6087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503155</v>
+        <v>503423</v>
       </c>
       <c r="R43" t="n">
-        <v>7035984</v>
+        <v>7036145</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6177,10 +6180,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131144267</v>
+        <v>131144282</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>80353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6188,31 +6191,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6220,10 +6218,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503564</v>
+        <v>503179</v>
       </c>
       <c r="R44" t="n">
-        <v>7036045</v>
+        <v>7035940</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6260,7 +6258,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6269,6 +6267,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6279,17 +6278,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6307,10 +6311,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131144263</v>
+        <v>131144276</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>80353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6318,31 +6322,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6350,10 +6349,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503363</v>
+        <v>503155</v>
       </c>
       <c r="R45" t="n">
-        <v>7035960</v>
+        <v>7035984</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6390,7 +6389,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6399,6 +6398,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6409,22 +6409,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6445,7 +6445,7 @@
         <v>131144295</v>
       </c>
       <c r="B46" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>131143981</v>
       </c>
       <c r="B47" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6699,10 +6699,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131144285</v>
+        <v>131144301</v>
       </c>
       <c r="B48" t="n">
-        <v>80351</v>
+        <v>91836</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6710,26 +6710,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503209</v>
+        <v>503583</v>
       </c>
       <c r="R48" t="n">
-        <v>7035903</v>
+        <v>7036073</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6775,11 +6775,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6797,22 +6792,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6830,10 +6820,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131143979</v>
+        <v>131144285</v>
       </c>
       <c r="B49" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6868,10 +6858,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503343</v>
+        <v>503209</v>
       </c>
       <c r="R49" t="n">
-        <v>7036013</v>
+        <v>7035903</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6904,6 +6894,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6956,10 +6951,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131144301</v>
+        <v>131143979</v>
       </c>
       <c r="B50" t="n">
-        <v>91834</v>
+        <v>80353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6967,26 +6962,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6994,10 +6989,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503583</v>
+        <v>503343</v>
       </c>
       <c r="R50" t="n">
-        <v>7036073</v>
+        <v>7036013</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7049,17 +7044,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7077,32 +7077,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131144300</v>
+        <v>131143983</v>
       </c>
       <c r="B51" t="n">
-        <v>80311</v>
+        <v>80353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503318</v>
+        <v>503376</v>
       </c>
       <c r="R51" t="n">
-        <v>7035950</v>
+        <v>7035991</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7151,11 +7151,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7208,32 +7203,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131143983</v>
+        <v>131144300</v>
       </c>
       <c r="B52" t="n">
-        <v>80351</v>
+        <v>80313</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7246,10 +7241,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503376</v>
+        <v>503318</v>
       </c>
       <c r="R52" t="n">
-        <v>7035991</v>
+        <v>7035950</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7282,6 +7277,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7337,7 +7337,7 @@
         <v>131144000</v>
       </c>
       <c r="B53" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>131144286</v>
       </c>
       <c r="B54" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>131144277</v>
       </c>
       <c r="B55" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>131143982</v>
       </c>
       <c r="B56" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>131143997</v>
       </c>
       <c r="B57" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>131144280</v>
       </c>
       <c r="B58" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>131144275</v>
       </c>
       <c r="B59" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>131144291</v>
       </c>
       <c r="B60" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>131143991</v>
       </c>
       <c r="B61" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>131144297</v>
       </c>
       <c r="B62" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>131143995</v>
       </c>
       <c r="B63" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>131144260</v>
       </c>
       <c r="B64" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>131144265</v>
       </c>
       <c r="B65" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8995,37 +8995,41 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131144283</v>
+        <v>131144268</v>
       </c>
       <c r="B66" t="n">
-        <v>80351</v>
+        <v>80382</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9033,10 +9037,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503196</v>
+        <v>503554</v>
       </c>
       <c r="R66" t="n">
-        <v>7035909</v>
+        <v>7036090</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9126,37 +9130,41 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131144001</v>
+        <v>131143968</v>
       </c>
       <c r="B67" t="n">
-        <v>79246</v>
+        <v>80382</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9164,10 +9172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503574</v>
+        <v>503216</v>
       </c>
       <c r="R67" t="n">
-        <v>7036113</v>
+        <v>7036102</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9202,6 +9210,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -9219,17 +9232,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9247,10 +9265,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131144298</v>
+        <v>131144283</v>
       </c>
       <c r="B68" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9285,10 +9303,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503191</v>
+        <v>503196</v>
       </c>
       <c r="R68" t="n">
-        <v>7035913</v>
+        <v>7035909</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9378,41 +9396,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131144268</v>
+        <v>131144001</v>
       </c>
       <c r="B69" t="n">
-        <v>80380</v>
+        <v>79248</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9420,10 +9434,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503554</v>
+        <v>503574</v>
       </c>
       <c r="R69" t="n">
-        <v>7036090</v>
+        <v>7036113</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9458,11 +9472,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9480,22 +9489,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9513,10 +9517,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131143968</v>
+        <v>131143974</v>
       </c>
       <c r="B70" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9543,11 +9547,7 @@
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503216</v>
+        <v>503424</v>
       </c>
       <c r="R70" t="n">
-        <v>7036102</v>
+        <v>7036001</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9648,32 +9648,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131143974</v>
+        <v>131144298</v>
       </c>
       <c r="B71" t="n">
-        <v>80380</v>
+        <v>80353</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503424</v>
+        <v>503191</v>
       </c>
       <c r="R71" t="n">
-        <v>7036001</v>
+        <v>7035913</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9782,7 +9782,7 @@
         <v>131144262</v>
       </c>
       <c r="B72" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>131144289</v>
       </c>
       <c r="B73" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>131144261</v>
       </c>
       <c r="B74" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10175,37 +10175,41 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131144302</v>
+        <v>131143970</v>
       </c>
       <c r="B75" t="n">
-        <v>79246</v>
+        <v>80382</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10213,10 +10217,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503606</v>
+        <v>503376</v>
       </c>
       <c r="R75" t="n">
-        <v>7036064</v>
+        <v>7035991</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10268,17 +10272,22 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10296,10 +10305,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131144273</v>
+        <v>131144302</v>
       </c>
       <c r="B76" t="n">
-        <v>80351</v>
+        <v>79248</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10307,21 +10316,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10334,10 +10343,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503267</v>
+        <v>503606</v>
       </c>
       <c r="R76" t="n">
-        <v>7036145</v>
+        <v>7036064</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10372,11 +10381,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -10394,22 +10398,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10427,41 +10426,37 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131143970</v>
+        <v>131144273</v>
       </c>
       <c r="B77" t="n">
-        <v>80380</v>
+        <v>80353</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10469,10 +10464,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503376</v>
+        <v>503267</v>
       </c>
       <c r="R77" t="n">
-        <v>7035991</v>
+        <v>7036145</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10505,6 +10500,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 379-2026 artfynd.xlsx
+++ b/artfynd/A 379-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131143977</v>
+        <v>131144266</v>
       </c>
       <c r="B2" t="n">
-        <v>80353</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503254</v>
+        <v>503547</v>
       </c>
       <c r="R2" t="n">
-        <v>7036092</v>
+        <v>7036037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,22 +777,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,39 +810,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131143975</v>
+        <v>131143977</v>
       </c>
       <c r="B3" t="n">
-        <v>80382</v>
+        <v>80354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503441</v>
+        <v>503254</v>
       </c>
       <c r="R3" t="n">
-        <v>7036004</v>
+        <v>7036092</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131143973</v>
+        <v>131143975</v>
       </c>
       <c r="B4" t="n">
-        <v>80382</v>
+        <v>80383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,11 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503418</v>
+        <v>503441</v>
       </c>
       <c r="R4" t="n">
-        <v>7036017</v>
+        <v>7036004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1076,42 +1080,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131144266</v>
+        <v>131143973</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>80383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1119,10 +1118,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503547</v>
+        <v>503418</v>
       </c>
       <c r="R5" t="n">
-        <v>7036037</v>
+        <v>7036017</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1158,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,6 +1167,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1178,22 +1178,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1214,7 +1214,7 @@
         <v>131143999</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>131143978</v>
       </c>
       <c r="B7" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>131144271</v>
       </c>
       <c r="B8" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>131144288</v>
       </c>
       <c r="B9" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>131144278</v>
       </c>
       <c r="B10" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>131143990</v>
       </c>
       <c r="B11" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>131144287</v>
       </c>
       <c r="B12" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>131144272</v>
       </c>
       <c r="B13" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>131143987</v>
       </c>
       <c r="B14" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2380,10 +2380,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131143984</v>
+        <v>131144279</v>
       </c>
       <c r="B15" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503375</v>
+        <v>503274</v>
       </c>
       <c r="R15" t="n">
-        <v>7036013</v>
+        <v>7035964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växer här på en rönn i äldre granskog.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2511,10 +2511,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131144279</v>
+        <v>131144296</v>
       </c>
       <c r="B16" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503274</v>
+        <v>503556</v>
       </c>
       <c r="R16" t="n">
-        <v>7035964</v>
+        <v>7036089</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131144296</v>
+        <v>131143980</v>
       </c>
       <c r="B17" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2672,7 +2672,11 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2680,10 +2684,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503556</v>
+        <v>503337</v>
       </c>
       <c r="R17" t="n">
-        <v>7036089</v>
+        <v>7036003</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2720,7 +2724,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Rikligt med lunglavsbålar på en rönn.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2736,6 +2740,11 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2773,10 +2782,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131143980</v>
+        <v>131144292</v>
       </c>
       <c r="B18" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2803,11 +2812,7 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2815,10 +2820,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503337</v>
+        <v>503355</v>
       </c>
       <c r="R18" t="n">
-        <v>7036003</v>
+        <v>7035956</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2855,7 +2860,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med lunglavsbålar på en rönn.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2871,11 +2876,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2913,10 +2913,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131144292</v>
+        <v>131143984</v>
       </c>
       <c r="B19" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503355</v>
+        <v>503375</v>
       </c>
       <c r="R19" t="n">
-        <v>7035956</v>
+        <v>7036013</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Växer här på en rönn i äldre granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3047,7 +3047,7 @@
         <v>131144274</v>
       </c>
       <c r="B20" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>131143986</v>
       </c>
       <c r="B21" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3310,41 +3310,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131143972</v>
+        <v>131143976</v>
       </c>
       <c r="B22" t="n">
-        <v>80382</v>
+        <v>80354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3352,10 +3348,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503377</v>
+        <v>503419</v>
       </c>
       <c r="R22" t="n">
-        <v>7036016</v>
+        <v>7036154</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3388,11 +3384,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3445,10 +3436,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131143976</v>
+        <v>131143989</v>
       </c>
       <c r="B23" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3483,10 +3474,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503419</v>
+        <v>503448</v>
       </c>
       <c r="R23" t="n">
-        <v>7036154</v>
+        <v>7036030</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3521,6 +3512,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lunglav på en gran vid en rönn med lunglav.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3538,22 +3534,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3571,10 +3567,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131143989</v>
+        <v>131143998</v>
       </c>
       <c r="B24" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3582,21 +3578,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3609,10 +3605,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503448</v>
+        <v>503444</v>
       </c>
       <c r="R24" t="n">
-        <v>7036030</v>
+        <v>7036006</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3649,7 +3645,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Lunglav på en gran vid en rönn med lunglav.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3677,14 +3673,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3702,37 +3693,41 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131143998</v>
+        <v>131143972</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>80383</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3740,10 +3735,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503444</v>
+        <v>503377</v>
       </c>
       <c r="R25" t="n">
-        <v>7036006</v>
+        <v>7036016</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3780,7 +3775,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3800,17 +3795,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
         <v>131144299</v>
       </c>
       <c r="B26" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>131144290</v>
       </c>
       <c r="B27" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>131144284</v>
       </c>
       <c r="B28" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>131143988</v>
       </c>
       <c r="B29" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131144293</v>
+        <v>131143993</v>
       </c>
       <c r="B30" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4358,21 +4358,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503484</v>
+        <v>503307</v>
       </c>
       <c r="R30" t="n">
-        <v>7036019</v>
+        <v>7036124</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4445,22 +4445,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4478,10 +4473,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131143993</v>
+        <v>131144281</v>
       </c>
       <c r="B31" t="n">
-        <v>79248</v>
+        <v>80354</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4489,21 +4484,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4516,10 +4511,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503307</v>
+        <v>503194</v>
       </c>
       <c r="R31" t="n">
-        <v>7036124</v>
+        <v>7035963</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4556,7 +4551,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4576,17 +4571,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131144281</v>
+        <v>131143994</v>
       </c>
       <c r="B32" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4615,21 +4615,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503194</v>
+        <v>503252</v>
       </c>
       <c r="R32" t="n">
-        <v>7035963</v>
+        <v>7036082</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4702,22 +4702,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4735,10 +4730,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131143994</v>
+        <v>131144293</v>
       </c>
       <c r="B33" t="n">
-        <v>79248</v>
+        <v>80354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4746,21 +4741,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4773,10 +4768,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503252</v>
+        <v>503484</v>
       </c>
       <c r="R33" t="n">
-        <v>7036082</v>
+        <v>7036019</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4813,7 +4808,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4833,17 +4828,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131143996</v>
+        <v>131144259</v>
       </c>
       <c r="B34" t="n">
-        <v>79248</v>
+        <v>91817</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4872,28 +4872,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503386</v>
+        <v>503326</v>
       </c>
       <c r="R34" t="n">
-        <v>7036016</v>
+        <v>7035948</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4941,11 +4941,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4961,11 +4956,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
-        </is>
-      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4978,12 +4968,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5001,10 +4991,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131144264</v>
+        <v>131143996</v>
       </c>
       <c r="B35" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5012,29 +5002,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5044,10 +5033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503447</v>
+        <v>503386</v>
       </c>
       <c r="R35" t="n">
-        <v>7035991</v>
+        <v>7036016</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5084,7 +5073,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5093,6 +5082,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5101,6 +5091,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
+        </is>
+      </c>
       <c r="AJ35" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5111,9 +5106,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5131,10 +5131,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131143967</v>
+        <v>131144294</v>
       </c>
       <c r="B36" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5142,31 +5142,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5174,10 +5169,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503201</v>
+        <v>503563</v>
       </c>
       <c r="R36" t="n">
-        <v>7036058</v>
+        <v>7036044</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5214,7 +5209,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5223,6 +5218,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5231,29 +5227,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5271,10 +5262,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131144294</v>
+        <v>131144264</v>
       </c>
       <c r="B37" t="n">
-        <v>80353</v>
+        <v>57887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5282,26 +5273,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5309,10 +5305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503563</v>
+        <v>503447</v>
       </c>
       <c r="R37" t="n">
-        <v>7036044</v>
+        <v>7035991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5349,7 +5345,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5358,7 +5354,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5369,22 +5364,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5402,10 +5392,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131144269</v>
+        <v>131143967</v>
       </c>
       <c r="B38" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5413,26 +5403,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5440,10 +5435,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503190</v>
+        <v>503201</v>
       </c>
       <c r="R38" t="n">
-        <v>7035938</v>
+        <v>7036058</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5480,7 +5475,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5489,7 +5484,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5498,24 +5492,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5533,10 +5532,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131144259</v>
+        <v>131144269</v>
       </c>
       <c r="B39" t="n">
-        <v>91816</v>
+        <v>80355</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5544,30 +5543,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5575,10 +5570,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503326</v>
+        <v>503190</v>
       </c>
       <c r="R39" t="n">
-        <v>7035948</v>
+        <v>7035938</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5613,6 +5608,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5630,22 +5630,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131143992</v>
+        <v>131144267</v>
       </c>
       <c r="B40" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5674,26 +5674,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5701,10 +5706,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503345</v>
+        <v>503564</v>
       </c>
       <c r="R40" t="n">
-        <v>7036137</v>
+        <v>7036045</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5739,13 +5744,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5784,10 +5793,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131144267</v>
+        <v>131144263</v>
       </c>
       <c r="B41" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5817,7 +5826,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5827,10 +5836,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503564</v>
+        <v>503363</v>
       </c>
       <c r="R41" t="n">
-        <v>7036045</v>
+        <v>7035960</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5867,7 +5876,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5894,9 +5903,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5914,10 +5928,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131144263</v>
+        <v>131143992</v>
       </c>
       <c r="B42" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5925,31 +5939,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5957,10 +5966,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503363</v>
+        <v>503345</v>
       </c>
       <c r="R42" t="n">
-        <v>7035960</v>
+        <v>7036137</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5995,17 +6004,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6024,14 +6029,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6052,7 +6052,7 @@
         <v>131144270</v>
       </c>
       <c r="B43" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>131144282</v>
       </c>
       <c r="B44" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>131144276</v>
       </c>
       <c r="B45" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>131144295</v>
       </c>
       <c r="B46" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>131143981</v>
       </c>
       <c r="B47" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>131144301</v>
       </c>
       <c r="B48" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>131144285</v>
       </c>
       <c r="B49" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>131143979</v>
       </c>
       <c r="B50" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>131143983</v>
       </c>
       <c r="B51" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>131144300</v>
       </c>
       <c r="B52" t="n">
-        <v>80313</v>
+        <v>80314</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>131144000</v>
       </c>
       <c r="B53" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>131144286</v>
       </c>
       <c r="B54" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>131144277</v>
       </c>
       <c r="B55" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>131143982</v>
       </c>
       <c r="B56" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>131143997</v>
       </c>
       <c r="B57" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>131144280</v>
       </c>
       <c r="B58" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>131144275</v>
       </c>
       <c r="B59" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>131144291</v>
       </c>
       <c r="B60" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>131143991</v>
       </c>
       <c r="B61" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>131144297</v>
       </c>
       <c r="B62" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>131143995</v>
       </c>
       <c r="B63" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>131144260</v>
       </c>
       <c r="B64" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>131144265</v>
       </c>
       <c r="B65" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>131144268</v>
       </c>
       <c r="B66" t="n">
-        <v>80382</v>
+        <v>80383</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>131143968</v>
       </c>
       <c r="B67" t="n">
-        <v>80382</v>
+        <v>80383</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>131144283</v>
       </c>
       <c r="B68" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>131144001</v>
       </c>
       <c r="B69" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>131143974</v>
       </c>
       <c r="B70" t="n">
-        <v>80382</v>
+        <v>80383</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>131144298</v>
       </c>
       <c r="B71" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>131144262</v>
       </c>
       <c r="B72" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>131144289</v>
       </c>
       <c r="B73" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>131144261</v>
       </c>
       <c r="B74" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>131143970</v>
       </c>
       <c r="B75" t="n">
-        <v>80382</v>
+        <v>80383</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>131144302</v>
       </c>
       <c r="B76" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>131144273</v>
       </c>
       <c r="B77" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 379-2026 artfynd.xlsx
+++ b/artfynd/A 379-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131144266</v>
+        <v>131143977</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503547</v>
+        <v>503254</v>
       </c>
       <c r="R2" t="n">
-        <v>7036037</v>
+        <v>7036092</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,22 +777,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,39 +810,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131143977</v>
+        <v>131143975</v>
       </c>
       <c r="B3" t="n">
-        <v>80354</v>
+        <v>80383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503254</v>
+        <v>503441</v>
       </c>
       <c r="R3" t="n">
-        <v>7036092</v>
+        <v>7036004</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131143975</v>
+        <v>131143973</v>
       </c>
       <c r="B4" t="n">
         <v>80383</v>
@@ -975,11 +975,7 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -987,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503441</v>
+        <v>503418</v>
       </c>
       <c r="R4" t="n">
-        <v>7036004</v>
+        <v>7036017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1080,37 +1076,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131143973</v>
+        <v>131144266</v>
       </c>
       <c r="B5" t="n">
-        <v>80383</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1118,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503418</v>
+        <v>503547</v>
       </c>
       <c r="R5" t="n">
-        <v>7036017</v>
+        <v>7036037</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1158,7 +1159,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,7 +1168,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1178,22 +1178,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131143976</v>
+        <v>131143998</v>
       </c>
       <c r="B22" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503419</v>
+        <v>503444</v>
       </c>
       <c r="R22" t="n">
-        <v>7036154</v>
+        <v>7036006</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3386,6 +3386,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3403,22 +3408,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3436,37 +3436,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131143989</v>
+        <v>131143972</v>
       </c>
       <c r="B23" t="n">
-        <v>80354</v>
+        <v>80383</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3474,10 +3478,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503448</v>
+        <v>503377</v>
       </c>
       <c r="R23" t="n">
-        <v>7036030</v>
+        <v>7036016</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3514,7 +3518,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Lunglav på en gran vid en rönn med lunglav.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3534,22 +3538,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3567,10 +3571,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131143998</v>
+        <v>131143976</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3578,21 +3582,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3605,10 +3609,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503444</v>
+        <v>503419</v>
       </c>
       <c r="R24" t="n">
-        <v>7036006</v>
+        <v>7036154</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3643,11 +3647,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3665,17 +3664,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3693,41 +3697,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131143972</v>
+        <v>131143989</v>
       </c>
       <c r="B25" t="n">
-        <v>80383</v>
+        <v>80354</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503377</v>
+        <v>503448</v>
       </c>
       <c r="R25" t="n">
-        <v>7036016</v>
+        <v>7036030</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Lunglav på en gran vid en rönn med lunglav.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3795,22 +3795,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131144281</v>
+        <v>131143994</v>
       </c>
       <c r="B31" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503194</v>
+        <v>503252</v>
       </c>
       <c r="R31" t="n">
-        <v>7035963</v>
+        <v>7036082</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4571,22 +4571,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4604,10 +4599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131143994</v>
+        <v>131144281</v>
       </c>
       <c r="B32" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4615,21 +4610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4642,10 +4637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503252</v>
+        <v>503194</v>
       </c>
       <c r="R32" t="n">
-        <v>7036082</v>
+        <v>7035963</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4682,7 +4677,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4702,17 +4697,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131143996</v>
+        <v>131144269</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>80355</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5002,30 +5002,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5033,10 +5029,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503386</v>
+        <v>503190</v>
       </c>
       <c r="R35" t="n">
-        <v>7036016</v>
+        <v>7035938</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5073,7 +5069,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5091,29 +5087,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
-        </is>
-      </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5532,10 +5523,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131144269</v>
+        <v>131143996</v>
       </c>
       <c r="B39" t="n">
-        <v>80355</v>
+        <v>79249</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5543,26 +5534,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5570,10 +5565,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503190</v>
+        <v>503386</v>
       </c>
       <c r="R39" t="n">
-        <v>7035938</v>
+        <v>7036016</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5610,7 +5605,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5628,24 +5623,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
+        </is>
+      </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131144267</v>
+        <v>131143992</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5674,31 +5674,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5706,10 +5701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503564</v>
+        <v>503345</v>
       </c>
       <c r="R40" t="n">
-        <v>7036045</v>
+        <v>7036137</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5744,17 +5739,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5793,10 +5784,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131144263</v>
+        <v>131144270</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5804,31 +5795,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5836,10 +5822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503363</v>
+        <v>503423</v>
       </c>
       <c r="R41" t="n">
-        <v>7035960</v>
+        <v>7036145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5876,7 +5862,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5885,6 +5871,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5895,22 +5882,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5928,10 +5915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131143992</v>
+        <v>131144282</v>
       </c>
       <c r="B42" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5939,21 +5926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5966,10 +5953,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503345</v>
+        <v>503179</v>
       </c>
       <c r="R42" t="n">
-        <v>7036137</v>
+        <v>7035940</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6004,6 +5991,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6021,17 +6013,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6049,7 +6046,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131144270</v>
+        <v>131144276</v>
       </c>
       <c r="B43" t="n">
         <v>80354</v>
@@ -6087,10 +6084,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503423</v>
+        <v>503155</v>
       </c>
       <c r="R43" t="n">
-        <v>7036145</v>
+        <v>7035984</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6180,10 +6177,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131144282</v>
+        <v>131144267</v>
       </c>
       <c r="B44" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6191,26 +6188,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6218,10 +6220,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503179</v>
+        <v>503564</v>
       </c>
       <c r="R44" t="n">
-        <v>7035940</v>
+        <v>7036045</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6258,7 +6260,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6267,7 +6269,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6278,22 +6279,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6311,10 +6307,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131144276</v>
+        <v>131144263</v>
       </c>
       <c r="B45" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6322,26 +6318,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6349,10 +6350,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503155</v>
+        <v>503363</v>
       </c>
       <c r="R45" t="n">
-        <v>7035984</v>
+        <v>7035960</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6389,7 +6390,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6398,7 +6399,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6409,22 +6409,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -7717,10 +7717,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131143982</v>
+        <v>131144260</v>
       </c>
       <c r="B56" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7728,26 +7728,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7755,10 +7760,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503364</v>
+        <v>503332</v>
       </c>
       <c r="R56" t="n">
-        <v>7035989</v>
+        <v>7035948</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7793,13 +7798,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7810,22 +7819,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7843,10 +7852,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131143997</v>
+        <v>131144265</v>
       </c>
       <c r="B57" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7854,26 +7863,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7881,10 +7895,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503416</v>
+        <v>503516</v>
       </c>
       <c r="R57" t="n">
-        <v>7036029</v>
+        <v>7036022</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7919,13 +7933,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7964,7 +7982,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131144280</v>
+        <v>131143982</v>
       </c>
       <c r="B58" t="n">
         <v>80354</v>
@@ -8002,10 +8020,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503251</v>
+        <v>503364</v>
       </c>
       <c r="R58" t="n">
-        <v>7035966</v>
+        <v>7035989</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8038,11 +8056,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8095,7 +8108,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131144275</v>
+        <v>131144280</v>
       </c>
       <c r="B59" t="n">
         <v>80354</v>
@@ -8133,10 +8146,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503195</v>
+        <v>503251</v>
       </c>
       <c r="R59" t="n">
-        <v>7036062</v>
+        <v>7035966</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8226,7 +8239,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131144291</v>
+        <v>131144275</v>
       </c>
       <c r="B60" t="n">
         <v>80354</v>
@@ -8264,10 +8277,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503317</v>
+        <v>503195</v>
       </c>
       <c r="R60" t="n">
-        <v>7035948</v>
+        <v>7036062</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8357,10 +8370,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131143991</v>
+        <v>131144291</v>
       </c>
       <c r="B61" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8368,21 +8381,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8395,10 +8408,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503400</v>
+        <v>503317</v>
       </c>
       <c r="R61" t="n">
-        <v>7036159</v>
+        <v>7035948</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8433,6 +8446,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8450,17 +8468,22 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8609,7 +8632,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131143995</v>
+        <v>131143997</v>
       </c>
       <c r="B63" t="n">
         <v>79249</v>
@@ -8647,10 +8670,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503216</v>
+        <v>503416</v>
       </c>
       <c r="R63" t="n">
-        <v>7036078</v>
+        <v>7036029</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8730,10 +8753,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131144260</v>
+        <v>131143991</v>
       </c>
       <c r="B64" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8741,31 +8764,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8773,10 +8791,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503332</v>
+        <v>503400</v>
       </c>
       <c r="R64" t="n">
-        <v>7035948</v>
+        <v>7036159</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8811,17 +8829,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8840,14 +8854,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8865,10 +8874,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131144265</v>
+        <v>131143995</v>
       </c>
       <c r="B65" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8876,31 +8885,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8908,10 +8912,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503516</v>
+        <v>503216</v>
       </c>
       <c r="R65" t="n">
-        <v>7036022</v>
+        <v>7036078</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8946,17 +8950,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -10175,41 +10175,37 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131143970</v>
+        <v>131144302</v>
       </c>
       <c r="B75" t="n">
-        <v>80383</v>
+        <v>79249</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10217,10 +10213,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503376</v>
+        <v>503606</v>
       </c>
       <c r="R75" t="n">
-        <v>7035991</v>
+        <v>7036064</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10272,22 +10268,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10305,37 +10296,41 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131144302</v>
+        <v>131143970</v>
       </c>
       <c r="B76" t="n">
-        <v>79249</v>
+        <v>80383</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10343,10 +10338,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503606</v>
+        <v>503376</v>
       </c>
       <c r="R76" t="n">
-        <v>7036064</v>
+        <v>7035991</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10398,17 +10393,22 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>

--- a/artfynd/A 379-2026 artfynd.xlsx
+++ b/artfynd/A 379-2026 artfynd.xlsx
@@ -675,39 +675,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131143977</v>
+        <v>131143975</v>
       </c>
       <c r="B2" t="n">
-        <v>80354</v>
+        <v>80383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503254</v>
+        <v>503441</v>
       </c>
       <c r="R2" t="n">
-        <v>7036092</v>
+        <v>7036004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -810,39 +810,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131143975</v>
+        <v>131143977</v>
       </c>
       <c r="B3" t="n">
-        <v>80383</v>
+        <v>80354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503441</v>
+        <v>503254</v>
       </c>
       <c r="R3" t="n">
-        <v>7036004</v>
+        <v>7036092</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1332,7 +1332,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131143978</v>
+        <v>131144271</v>
       </c>
       <c r="B7" t="n">
         <v>80354</v>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503218</v>
+        <v>503292</v>
       </c>
       <c r="R7" t="n">
-        <v>7036101</v>
+        <v>7036126</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131144271</v>
+        <v>131144278</v>
       </c>
       <c r="B8" t="n">
         <v>80354</v>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503292</v>
+        <v>503277</v>
       </c>
       <c r="R8" t="n">
-        <v>7036126</v>
+        <v>7035964</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131144278</v>
+        <v>131143978</v>
       </c>
       <c r="B10" t="n">
         <v>80354</v>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503277</v>
+        <v>503218</v>
       </c>
       <c r="R10" t="n">
-        <v>7035964</v>
+        <v>7036101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1856,7 +1856,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131143990</v>
+        <v>131143987</v>
       </c>
       <c r="B11" t="n">
         <v>80354</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503447</v>
+        <v>503418</v>
       </c>
       <c r="R11" t="n">
-        <v>7036031</v>
+        <v>7036017</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131144287</v>
+        <v>131143990</v>
       </c>
       <c r="B12" t="n">
         <v>80354</v>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503222</v>
+        <v>503447</v>
       </c>
       <c r="R12" t="n">
-        <v>7035916</v>
+        <v>7036031</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131143987</v>
+        <v>131144287</v>
       </c>
       <c r="B14" t="n">
         <v>80354</v>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503418</v>
+        <v>503222</v>
       </c>
       <c r="R14" t="n">
-        <v>7036017</v>
+        <v>7035916</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131144296</v>
+        <v>131144292</v>
       </c>
       <c r="B16" t="n">
         <v>80354</v>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503556</v>
+        <v>503355</v>
       </c>
       <c r="R16" t="n">
-        <v>7036089</v>
+        <v>7035956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131143980</v>
+        <v>131144296</v>
       </c>
       <c r="B17" t="n">
         <v>80354</v>
@@ -2672,11 +2672,7 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2684,10 +2680,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503337</v>
+        <v>503556</v>
       </c>
       <c r="R17" t="n">
-        <v>7036003</v>
+        <v>7036089</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2724,7 +2720,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med lunglavsbålar på en rönn.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2740,11 +2736,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2782,7 +2773,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131144292</v>
+        <v>131143984</v>
       </c>
       <c r="B18" t="n">
         <v>80354</v>
@@ -2820,10 +2811,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503355</v>
+        <v>503375</v>
       </c>
       <c r="R18" t="n">
-        <v>7035956</v>
+        <v>7036013</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2860,7 +2851,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Växer här på en rönn i äldre granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2913,7 +2904,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131143984</v>
+        <v>131143980</v>
       </c>
       <c r="B19" t="n">
         <v>80354</v>
@@ -2943,7 +2934,11 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2951,10 +2946,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503375</v>
+        <v>503337</v>
       </c>
       <c r="R19" t="n">
-        <v>7036013</v>
+        <v>7036003</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2991,7 +2986,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Växer här på en rönn i äldre granskog.</t>
+          <t>Rikligt med lunglavsbålar på en rönn.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3007,6 +3002,11 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3310,10 +3310,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131143998</v>
+        <v>131143976</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503444</v>
+        <v>503419</v>
       </c>
       <c r="R22" t="n">
-        <v>7036006</v>
+        <v>7036154</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3386,11 +3386,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3408,17 +3403,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131143976</v>
+        <v>131143989</v>
       </c>
       <c r="B24" t="n">
         <v>80354</v>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503419</v>
+        <v>503448</v>
       </c>
       <c r="R24" t="n">
-        <v>7036154</v>
+        <v>7036030</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3647,6 +3647,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Lunglav på en gran vid en rönn med lunglav.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3664,22 +3669,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3697,10 +3702,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131143989</v>
+        <v>131143998</v>
       </c>
       <c r="B25" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3708,21 +3713,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3735,10 +3740,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503448</v>
+        <v>503444</v>
       </c>
       <c r="R25" t="n">
-        <v>7036030</v>
+        <v>7036006</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3775,7 +3780,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Lunglav på en gran vid en rönn med lunglav.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3803,14 +3808,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131144299</v>
+        <v>131144284</v>
       </c>
       <c r="B26" t="n">
         <v>80354</v>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503345</v>
+        <v>503203</v>
       </c>
       <c r="R26" t="n">
-        <v>7035956</v>
+        <v>7035913</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3959,7 +3959,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131144290</v>
+        <v>131144299</v>
       </c>
       <c r="B27" t="n">
         <v>80354</v>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503313</v>
+        <v>503345</v>
       </c>
       <c r="R27" t="n">
-        <v>7035948</v>
+        <v>7035956</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131144284</v>
+        <v>131144290</v>
       </c>
       <c r="B28" t="n">
         <v>80354</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503203</v>
+        <v>503313</v>
       </c>
       <c r="R28" t="n">
-        <v>7035913</v>
+        <v>7035948</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -5253,10 +5253,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131144264</v>
+        <v>131143996</v>
       </c>
       <c r="B37" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5264,29 +5264,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5296,10 +5295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503447</v>
+        <v>503386</v>
       </c>
       <c r="R37" t="n">
-        <v>7035991</v>
+        <v>7036016</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5336,7 +5335,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5345,6 +5344,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5353,6 +5353,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
+        </is>
+      </c>
       <c r="AJ37" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5363,9 +5368,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5383,7 +5393,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131143967</v>
+        <v>131144264</v>
       </c>
       <c r="B38" t="n">
         <v>57887</v>
@@ -5416,7 +5426,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5426,10 +5436,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503201</v>
+        <v>503447</v>
       </c>
       <c r="R38" t="n">
-        <v>7036058</v>
+        <v>7035991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5466,7 +5476,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5483,11 +5493,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ38" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5498,14 +5503,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5523,10 +5523,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131143996</v>
+        <v>131143967</v>
       </c>
       <c r="B39" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5534,28 +5534,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5565,10 +5566,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503386</v>
+        <v>503201</v>
       </c>
       <c r="R39" t="n">
-        <v>7036016</v>
+        <v>7036058</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5605,7 +5606,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5614,7 +5615,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
+          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5915,7 +5915,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131144282</v>
+        <v>131144276</v>
       </c>
       <c r="B42" t="n">
         <v>80354</v>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503179</v>
+        <v>503155</v>
       </c>
       <c r="R42" t="n">
-        <v>7035940</v>
+        <v>7035984</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6046,7 +6046,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131144276</v>
+        <v>131144282</v>
       </c>
       <c r="B43" t="n">
         <v>80354</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503155</v>
+        <v>503179</v>
       </c>
       <c r="R43" t="n">
-        <v>7035984</v>
+        <v>7035940</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6820,7 +6820,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131144285</v>
+        <v>131143979</v>
       </c>
       <c r="B49" t="n">
         <v>80354</v>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503209</v>
+        <v>503343</v>
       </c>
       <c r="R49" t="n">
-        <v>7035903</v>
+        <v>7036013</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6894,11 +6894,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6951,7 +6946,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131143979</v>
+        <v>131144285</v>
       </c>
       <c r="B50" t="n">
         <v>80354</v>
@@ -6989,10 +6984,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503343</v>
+        <v>503209</v>
       </c>
       <c r="R50" t="n">
-        <v>7036013</v>
+        <v>7035903</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7025,6 +7020,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7455,7 +7455,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131144286</v>
+        <v>131144277</v>
       </c>
       <c r="B54" t="n">
         <v>80354</v>
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503215</v>
+        <v>503292</v>
       </c>
       <c r="R54" t="n">
-        <v>7035916</v>
+        <v>7035968</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7586,7 +7586,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131144277</v>
+        <v>131144286</v>
       </c>
       <c r="B55" t="n">
         <v>80354</v>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503292</v>
+        <v>503215</v>
       </c>
       <c r="R55" t="n">
-        <v>7035968</v>
+        <v>7035916</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7717,10 +7717,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131144260</v>
+        <v>131144297</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7728,31 +7728,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7760,10 +7755,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503332</v>
+        <v>503354</v>
       </c>
       <c r="R56" t="n">
-        <v>7035948</v>
+        <v>7036143</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7800,7 +7795,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7809,6 +7804,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7819,22 +7815,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7852,10 +7848,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131144265</v>
+        <v>131144275</v>
       </c>
       <c r="B57" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7863,31 +7859,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7895,10 +7886,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503516</v>
+        <v>503195</v>
       </c>
       <c r="R57" t="n">
-        <v>7036022</v>
+        <v>7036062</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7935,7 +7926,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7944,6 +7935,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7954,17 +7946,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8108,7 +8105,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131144280</v>
+        <v>131144291</v>
       </c>
       <c r="B59" t="n">
         <v>80354</v>
@@ -8146,10 +8143,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503251</v>
+        <v>503317</v>
       </c>
       <c r="R59" t="n">
-        <v>7035966</v>
+        <v>7035948</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8239,7 +8236,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131144275</v>
+        <v>131144280</v>
       </c>
       <c r="B60" t="n">
         <v>80354</v>
@@ -8277,10 +8274,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503195</v>
+        <v>503251</v>
       </c>
       <c r="R60" t="n">
-        <v>7036062</v>
+        <v>7035966</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8370,10 +8367,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131144291</v>
+        <v>131144260</v>
       </c>
       <c r="B61" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8381,26 +8378,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8408,7 +8410,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503317</v>
+        <v>503332</v>
       </c>
       <c r="R61" t="n">
         <v>7035948</v>
@@ -8448,7 +8450,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8457,7 +8459,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -8468,22 +8469,22 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8501,10 +8502,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131144297</v>
+        <v>131144265</v>
       </c>
       <c r="B62" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8512,26 +8513,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8539,10 +8545,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503354</v>
+        <v>503516</v>
       </c>
       <c r="R62" t="n">
-        <v>7036143</v>
+        <v>7036022</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8579,7 +8585,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8588,7 +8594,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8599,22 +8604,17 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8995,41 +8995,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131144268</v>
+        <v>131144001</v>
       </c>
       <c r="B66" t="n">
-        <v>80383</v>
+        <v>79249</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9037,10 +9033,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503554</v>
+        <v>503574</v>
       </c>
       <c r="R66" t="n">
-        <v>7036090</v>
+        <v>7036113</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9075,11 +9071,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9097,22 +9088,17 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9130,7 +9116,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131143968</v>
+        <v>131144268</v>
       </c>
       <c r="B67" t="n">
         <v>80383</v>
@@ -9172,10 +9158,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503216</v>
+        <v>503554</v>
       </c>
       <c r="R67" t="n">
-        <v>7036102</v>
+        <v>7036090</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9265,32 +9251,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131144283</v>
+        <v>131143974</v>
       </c>
       <c r="B68" t="n">
-        <v>80354</v>
+        <v>80383</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9303,10 +9289,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503196</v>
+        <v>503424</v>
       </c>
       <c r="R68" t="n">
-        <v>7035909</v>
+        <v>7036001</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9396,10 +9382,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131144001</v>
+        <v>131144298</v>
       </c>
       <c r="B69" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9407,21 +9393,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9434,10 +9420,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503574</v>
+        <v>503191</v>
       </c>
       <c r="R69" t="n">
-        <v>7036113</v>
+        <v>7035913</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9472,6 +9458,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9489,17 +9480,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9517,32 +9513,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131143974</v>
+        <v>131144283</v>
       </c>
       <c r="B70" t="n">
-        <v>80383</v>
+        <v>80354</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9555,10 +9551,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503424</v>
+        <v>503196</v>
       </c>
       <c r="R70" t="n">
-        <v>7036001</v>
+        <v>7035909</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9648,37 +9644,41 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131144298</v>
+        <v>131143968</v>
       </c>
       <c r="B71" t="n">
-        <v>80354</v>
+        <v>80383</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503191</v>
+        <v>503216</v>
       </c>
       <c r="R71" t="n">
-        <v>7035913</v>
+        <v>7036102</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -10296,41 +10296,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131143970</v>
+        <v>131144273</v>
       </c>
       <c r="B76" t="n">
-        <v>80383</v>
+        <v>80354</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10338,10 +10334,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503376</v>
+        <v>503267</v>
       </c>
       <c r="R76" t="n">
-        <v>7035991</v>
+        <v>7036145</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10374,6 +10370,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10426,37 +10427,41 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131144273</v>
+        <v>131143970</v>
       </c>
       <c r="B77" t="n">
-        <v>80354</v>
+        <v>80383</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10464,10 +10469,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503267</v>
+        <v>503376</v>
       </c>
       <c r="R77" t="n">
-        <v>7036145</v>
+        <v>7035991</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10500,11 +10505,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 379-2026 artfynd.xlsx
+++ b/artfynd/A 379-2026 artfynd.xlsx
@@ -675,39 +675,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131143975</v>
+        <v>131143977</v>
       </c>
       <c r="B2" t="n">
-        <v>80383</v>
+        <v>80355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503441</v>
+        <v>503254</v>
       </c>
       <c r="R2" t="n">
-        <v>7036004</v>
+        <v>7036092</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -810,39 +810,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131143977</v>
+        <v>131143975</v>
       </c>
       <c r="B3" t="n">
-        <v>80354</v>
+        <v>80384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503254</v>
+        <v>503441</v>
       </c>
       <c r="R3" t="n">
-        <v>7036092</v>
+        <v>7036004</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -948,7 +948,7 @@
         <v>131143973</v>
       </c>
       <c r="B4" t="n">
-        <v>80383</v>
+        <v>80384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>131144266</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131143999</v>
+        <v>131143978</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>80355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503460</v>
+        <v>503218</v>
       </c>
       <c r="R6" t="n">
-        <v>7036014</v>
+        <v>7036101</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,6 +1287,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1304,17 +1309,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,7 +1345,7 @@
         <v>131144271</v>
       </c>
       <c r="B7" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1466,7 +1476,7 @@
         <v>131144278</v>
       </c>
       <c r="B8" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1594,10 +1604,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131144288</v>
+        <v>131143999</v>
       </c>
       <c r="B9" t="n">
-        <v>80354</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,21 +1615,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1632,10 +1642,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503258</v>
+        <v>503460</v>
       </c>
       <c r="R9" t="n">
-        <v>7035950</v>
+        <v>7036014</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1670,11 +1680,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1692,22 +1697,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131143978</v>
+        <v>131144288</v>
       </c>
       <c r="B10" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503218</v>
+        <v>503258</v>
       </c>
       <c r="R10" t="n">
-        <v>7036101</v>
+        <v>7035950</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131143987</v>
+        <v>131143990</v>
       </c>
       <c r="B11" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503418</v>
+        <v>503447</v>
       </c>
       <c r="R11" t="n">
-        <v>7036017</v>
+        <v>7036031</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131143990</v>
+        <v>131144287</v>
       </c>
       <c r="B12" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503447</v>
+        <v>503222</v>
       </c>
       <c r="R12" t="n">
-        <v>7036031</v>
+        <v>7035916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
         <v>131144272</v>
       </c>
       <c r="B13" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131144287</v>
+        <v>131143987</v>
       </c>
       <c r="B14" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503222</v>
+        <v>503418</v>
       </c>
       <c r="R14" t="n">
-        <v>7035916</v>
+        <v>7036017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2383,7 +2383,7 @@
         <v>131144279</v>
       </c>
       <c r="B15" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131144292</v>
+        <v>131144296</v>
       </c>
       <c r="B16" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503355</v>
+        <v>503556</v>
       </c>
       <c r="R16" t="n">
-        <v>7035956</v>
+        <v>7036089</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131144296</v>
+        <v>131143980</v>
       </c>
       <c r="B17" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2672,7 +2672,11 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2680,10 +2684,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503556</v>
+        <v>503337</v>
       </c>
       <c r="R17" t="n">
-        <v>7036089</v>
+        <v>7036003</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2720,7 +2724,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Rikligt med lunglavsbålar på en rönn.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2736,6 +2740,11 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2773,10 +2782,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131143984</v>
+        <v>131144292</v>
       </c>
       <c r="B18" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2811,10 +2820,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503375</v>
+        <v>503355</v>
       </c>
       <c r="R18" t="n">
-        <v>7036013</v>
+        <v>7035956</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2851,7 +2860,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Växer här på en rönn i äldre granskog.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2904,10 +2913,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131143980</v>
+        <v>131143984</v>
       </c>
       <c r="B19" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2934,11 +2943,7 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2946,10 +2951,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503337</v>
+        <v>503375</v>
       </c>
       <c r="R19" t="n">
-        <v>7036003</v>
+        <v>7036013</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2986,7 +2991,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med lunglavsbålar på en rönn.</t>
+          <t>Växer här på en rönn i äldre granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3002,11 +3007,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3047,7 +3047,7 @@
         <v>131144274</v>
       </c>
       <c r="B20" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>131143986</v>
       </c>
       <c r="B21" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3310,37 +3310,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131143976</v>
+        <v>131143972</v>
       </c>
       <c r="B22" t="n">
-        <v>80354</v>
+        <v>80384</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3348,10 +3352,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503419</v>
+        <v>503377</v>
       </c>
       <c r="R22" t="n">
-        <v>7036154</v>
+        <v>7036016</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3384,6 +3388,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3436,41 +3445,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131143972</v>
+        <v>131143976</v>
       </c>
       <c r="B23" t="n">
-        <v>80383</v>
+        <v>80355</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3478,10 +3483,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503377</v>
+        <v>503419</v>
       </c>
       <c r="R23" t="n">
-        <v>7036016</v>
+        <v>7036154</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3514,11 +3519,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3574,7 +3574,7 @@
         <v>131143989</v>
       </c>
       <c r="B24" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>131143998</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3828,10 +3828,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131144284</v>
+        <v>131144299</v>
       </c>
       <c r="B26" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503203</v>
+        <v>503345</v>
       </c>
       <c r="R26" t="n">
-        <v>7035913</v>
+        <v>7035956</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131144299</v>
+        <v>131144290</v>
       </c>
       <c r="B27" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503345</v>
+        <v>503313</v>
       </c>
       <c r="R27" t="n">
-        <v>7035956</v>
+        <v>7035948</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4090,10 +4090,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131144290</v>
+        <v>131144284</v>
       </c>
       <c r="B28" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503313</v>
+        <v>503203</v>
       </c>
       <c r="R28" t="n">
-        <v>7035948</v>
+        <v>7035913</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4224,7 +4224,7 @@
         <v>131143988</v>
       </c>
       <c r="B29" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>131143993</v>
       </c>
       <c r="B30" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131143994</v>
+        <v>131144281</v>
       </c>
       <c r="B31" t="n">
-        <v>79249</v>
+        <v>80355</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503252</v>
+        <v>503194</v>
       </c>
       <c r="R31" t="n">
-        <v>7036082</v>
+        <v>7035963</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4571,17 +4571,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4599,10 +4604,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131144281</v>
+        <v>131143994</v>
       </c>
       <c r="B32" t="n">
-        <v>80354</v>
+        <v>79250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4610,21 +4615,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4637,10 +4642,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503194</v>
+        <v>503252</v>
       </c>
       <c r="R32" t="n">
-        <v>7035963</v>
+        <v>7036082</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4677,7 +4682,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4697,22 +4702,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4733,7 +4733,7 @@
         <v>131144293</v>
       </c>
       <c r="B33" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131144259</v>
+        <v>131144269</v>
       </c>
       <c r="B34" t="n">
-        <v>91817</v>
+        <v>80356</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4872,30 +4872,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4903,10 +4899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503326</v>
+        <v>503190</v>
       </c>
       <c r="R34" t="n">
-        <v>7035948</v>
+        <v>7035938</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4941,6 +4937,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4958,22 +4959,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4991,10 +4992,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131144269</v>
+        <v>131144259</v>
       </c>
       <c r="B35" t="n">
-        <v>80355</v>
+        <v>91818</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5002,26 +5003,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5029,10 +5034,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503190</v>
+        <v>503326</v>
       </c>
       <c r="R35" t="n">
-        <v>7035938</v>
+        <v>7035948</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5067,11 +5072,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5089,22 +5089,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131144294</v>
+        <v>131144264</v>
       </c>
       <c r="B36" t="n">
-        <v>80354</v>
+        <v>57888</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5133,26 +5133,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5160,10 +5165,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503563</v>
+        <v>503447</v>
       </c>
       <c r="R36" t="n">
-        <v>7036044</v>
+        <v>7035991</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5200,7 +5205,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5209,7 +5214,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5220,22 +5224,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5253,10 +5252,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131143996</v>
+        <v>131143967</v>
       </c>
       <c r="B37" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5264,28 +5263,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503386</v>
+        <v>503201</v>
       </c>
       <c r="R37" t="n">
-        <v>7036016</v>
+        <v>7036058</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5344,7 +5344,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5355,7 +5354,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
+          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5370,12 +5369,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5393,10 +5392,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131144264</v>
+        <v>131143996</v>
       </c>
       <c r="B38" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5404,29 +5403,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5436,10 +5434,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503447</v>
+        <v>503386</v>
       </c>
       <c r="R38" t="n">
-        <v>7035991</v>
+        <v>7036016</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5476,7 +5474,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5485,6 +5483,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5493,6 +5492,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
+        </is>
+      </c>
       <c r="AJ38" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5503,9 +5507,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5523,10 +5532,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131143967</v>
+        <v>131144294</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>80355</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5534,31 +5543,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5566,10 +5570,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503201</v>
+        <v>503563</v>
       </c>
       <c r="R39" t="n">
-        <v>7036058</v>
+        <v>7036044</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5606,7 +5610,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5615,6 +5619,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5623,29 +5628,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5666,7 +5666,7 @@
         <v>131143992</v>
       </c>
       <c r="B40" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>131144270</v>
       </c>
       <c r="B41" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5915,10 +5915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131144276</v>
+        <v>131144282</v>
       </c>
       <c r="B42" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503155</v>
+        <v>503179</v>
       </c>
       <c r="R42" t="n">
-        <v>7035984</v>
+        <v>7035940</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6046,10 +6046,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131144282</v>
+        <v>131144276</v>
       </c>
       <c r="B43" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503179</v>
+        <v>503155</v>
       </c>
       <c r="R43" t="n">
-        <v>7035940</v>
+        <v>7035984</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6180,7 +6180,7 @@
         <v>131144267</v>
       </c>
       <c r="B44" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>131144263</v>
       </c>
       <c r="B45" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>131144295</v>
       </c>
       <c r="B46" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>131143981</v>
       </c>
       <c r="B47" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6699,10 +6699,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131144301</v>
+        <v>131144285</v>
       </c>
       <c r="B48" t="n">
-        <v>91837</v>
+        <v>80355</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6710,26 +6710,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503583</v>
+        <v>503209</v>
       </c>
       <c r="R48" t="n">
-        <v>7036073</v>
+        <v>7035903</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6775,6 +6775,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6792,17 +6797,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6823,7 +6833,7 @@
         <v>131143979</v>
       </c>
       <c r="B49" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6946,10 +6956,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131144285</v>
+        <v>131144301</v>
       </c>
       <c r="B50" t="n">
-        <v>80354</v>
+        <v>91838</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6957,26 +6967,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6984,10 +6994,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503209</v>
+        <v>503583</v>
       </c>
       <c r="R50" t="n">
-        <v>7035903</v>
+        <v>7036073</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7022,11 +7032,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -7044,22 +7049,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7080,7 +7080,7 @@
         <v>131143983</v>
       </c>
       <c r="B51" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>131144300</v>
       </c>
       <c r="B52" t="n">
-        <v>80314</v>
+        <v>80315</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>131144000</v>
       </c>
       <c r="B53" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7455,10 +7455,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131144277</v>
+        <v>131144286</v>
       </c>
       <c r="B54" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503292</v>
+        <v>503215</v>
       </c>
       <c r="R54" t="n">
-        <v>7035968</v>
+        <v>7035916</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7586,10 +7586,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131144286</v>
+        <v>131144277</v>
       </c>
       <c r="B55" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503215</v>
+        <v>503292</v>
       </c>
       <c r="R55" t="n">
-        <v>7035916</v>
+        <v>7035968</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7717,10 +7717,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131144297</v>
+        <v>131144260</v>
       </c>
       <c r="B56" t="n">
-        <v>80354</v>
+        <v>57888</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7728,26 +7728,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7755,10 +7760,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503354</v>
+        <v>503332</v>
       </c>
       <c r="R56" t="n">
-        <v>7036143</v>
+        <v>7035948</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7795,7 +7800,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7804,7 +7809,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7815,22 +7819,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7848,10 +7852,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131144275</v>
+        <v>131144265</v>
       </c>
       <c r="B57" t="n">
-        <v>80354</v>
+        <v>57888</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7859,26 +7863,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7886,10 +7895,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503195</v>
+        <v>503516</v>
       </c>
       <c r="R57" t="n">
-        <v>7036062</v>
+        <v>7036022</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7926,7 +7935,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7935,7 +7944,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7946,22 +7954,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7982,7 +7985,7 @@
         <v>131143982</v>
       </c>
       <c r="B58" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8105,10 +8108,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131144291</v>
+        <v>131143997</v>
       </c>
       <c r="B59" t="n">
-        <v>80354</v>
+        <v>79250</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8116,21 +8119,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8143,10 +8146,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503317</v>
+        <v>503416</v>
       </c>
       <c r="R59" t="n">
-        <v>7035948</v>
+        <v>7036029</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8181,11 +8184,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -8203,22 +8201,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8239,7 +8232,7 @@
         <v>131144280</v>
       </c>
       <c r="B60" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8367,10 +8360,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131144260</v>
+        <v>131144275</v>
       </c>
       <c r="B61" t="n">
-        <v>57887</v>
+        <v>80355</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8378,31 +8371,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8410,10 +8398,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503332</v>
+        <v>503195</v>
       </c>
       <c r="R61" t="n">
-        <v>7035948</v>
+        <v>7036062</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8450,7 +8438,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8459,6 +8447,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -8469,22 +8458,22 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8502,10 +8491,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131144265</v>
+        <v>131144291</v>
       </c>
       <c r="B62" t="n">
-        <v>57887</v>
+        <v>80355</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8513,31 +8502,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8545,10 +8529,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503516</v>
+        <v>503317</v>
       </c>
       <c r="R62" t="n">
-        <v>7036022</v>
+        <v>7035948</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8585,7 +8569,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8594,6 +8578,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8604,17 +8589,22 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8632,10 +8622,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131143997</v>
+        <v>131143991</v>
       </c>
       <c r="B63" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8670,10 +8660,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503416</v>
+        <v>503400</v>
       </c>
       <c r="R63" t="n">
-        <v>7036029</v>
+        <v>7036159</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8753,10 +8743,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131143991</v>
+        <v>131144297</v>
       </c>
       <c r="B64" t="n">
-        <v>79249</v>
+        <v>80355</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8764,21 +8754,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8791,10 +8781,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503400</v>
+        <v>503354</v>
       </c>
       <c r="R64" t="n">
-        <v>7036159</v>
+        <v>7036143</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8829,6 +8819,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8846,17 +8841,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8877,7 +8877,7 @@
         <v>131143995</v>
       </c>
       <c r="B65" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8995,37 +8995,41 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131144001</v>
+        <v>131144268</v>
       </c>
       <c r="B66" t="n">
-        <v>79249</v>
+        <v>80384</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9033,10 +9037,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503574</v>
+        <v>503554</v>
       </c>
       <c r="R66" t="n">
-        <v>7036113</v>
+        <v>7036090</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9071,6 +9075,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9088,17 +9097,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9116,10 +9130,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131144268</v>
+        <v>131143968</v>
       </c>
       <c r="B67" t="n">
-        <v>80383</v>
+        <v>80384</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9158,10 +9172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503554</v>
+        <v>503216</v>
       </c>
       <c r="R67" t="n">
-        <v>7036090</v>
+        <v>7036102</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9251,32 +9265,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131143974</v>
+        <v>131144283</v>
       </c>
       <c r="B68" t="n">
-        <v>80383</v>
+        <v>80355</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9289,10 +9303,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503424</v>
+        <v>503196</v>
       </c>
       <c r="R68" t="n">
-        <v>7036001</v>
+        <v>7035909</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9382,10 +9396,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131144298</v>
+        <v>131144001</v>
       </c>
       <c r="B69" t="n">
-        <v>80354</v>
+        <v>79250</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9393,21 +9407,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9420,10 +9434,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503191</v>
+        <v>503574</v>
       </c>
       <c r="R69" t="n">
-        <v>7035913</v>
+        <v>7036113</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9458,11 +9472,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9480,22 +9489,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9513,32 +9517,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131144283</v>
+        <v>131143974</v>
       </c>
       <c r="B70" t="n">
-        <v>80354</v>
+        <v>80384</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9551,10 +9555,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503196</v>
+        <v>503424</v>
       </c>
       <c r="R70" t="n">
-        <v>7035909</v>
+        <v>7036001</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9644,41 +9648,37 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131143968</v>
+        <v>131144298</v>
       </c>
       <c r="B71" t="n">
-        <v>80383</v>
+        <v>80355</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503216</v>
+        <v>503191</v>
       </c>
       <c r="R71" t="n">
-        <v>7036102</v>
+        <v>7035913</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9782,7 +9782,7 @@
         <v>131144262</v>
       </c>
       <c r="B72" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>131144289</v>
       </c>
       <c r="B73" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>131144261</v>
       </c>
       <c r="B74" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10175,37 +10175,41 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131144302</v>
+        <v>131143970</v>
       </c>
       <c r="B75" t="n">
-        <v>79249</v>
+        <v>80384</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10213,10 +10217,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503606</v>
+        <v>503376</v>
       </c>
       <c r="R75" t="n">
-        <v>7036064</v>
+        <v>7035991</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10268,17 +10272,22 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10296,10 +10305,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131144273</v>
+        <v>131144302</v>
       </c>
       <c r="B76" t="n">
-        <v>80354</v>
+        <v>79250</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10307,21 +10316,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10334,10 +10343,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503267</v>
+        <v>503606</v>
       </c>
       <c r="R76" t="n">
-        <v>7036145</v>
+        <v>7036064</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10372,11 +10381,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -10394,22 +10398,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10427,41 +10426,37 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131143970</v>
+        <v>131144273</v>
       </c>
       <c r="B77" t="n">
-        <v>80383</v>
+        <v>80355</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10469,10 +10464,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503376</v>
+        <v>503267</v>
       </c>
       <c r="R77" t="n">
-        <v>7035991</v>
+        <v>7036145</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10505,6 +10500,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 379-2026 artfynd.xlsx
+++ b/artfynd/A 379-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131143977</v>
+        <v>131144266</v>
       </c>
       <c r="B2" t="n">
-        <v>80355</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503254</v>
+        <v>503547</v>
       </c>
       <c r="R2" t="n">
-        <v>7036092</v>
+        <v>7036037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,22 +777,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,39 +810,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131143975</v>
+        <v>131143977</v>
       </c>
       <c r="B3" t="n">
-        <v>80384</v>
+        <v>80355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503441</v>
+        <v>503254</v>
       </c>
       <c r="R3" t="n">
-        <v>7036004</v>
+        <v>7036092</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131143973</v>
+        <v>131143975</v>
       </c>
       <c r="B4" t="n">
         <v>80384</v>
@@ -975,7 +975,11 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503418</v>
+        <v>503441</v>
       </c>
       <c r="R4" t="n">
-        <v>7036017</v>
+        <v>7036004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1076,42 +1080,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131144266</v>
+        <v>131143973</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>80384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1119,10 +1118,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503547</v>
+        <v>503418</v>
       </c>
       <c r="R5" t="n">
-        <v>7036037</v>
+        <v>7036017</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1158,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,6 +1167,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1178,22 +1178,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131143978</v>
+        <v>131143999</v>
       </c>
       <c r="B6" t="n">
-        <v>80355</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503218</v>
+        <v>503460</v>
       </c>
       <c r="R6" t="n">
-        <v>7036101</v>
+        <v>7036014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,11 +1287,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1309,22 +1304,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1342,7 +1332,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131144271</v>
+        <v>131143978</v>
       </c>
       <c r="B7" t="n">
         <v>80355</v>
@@ -1380,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503292</v>
+        <v>503218</v>
       </c>
       <c r="R7" t="n">
-        <v>7036126</v>
+        <v>7036101</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1473,7 +1463,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131144278</v>
+        <v>131144271</v>
       </c>
       <c r="B8" t="n">
         <v>80355</v>
@@ -1511,10 +1501,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503277</v>
+        <v>503292</v>
       </c>
       <c r="R8" t="n">
-        <v>7035964</v>
+        <v>7036126</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1604,10 +1594,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131143999</v>
+        <v>131144288</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>80355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,21 +1605,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1642,10 +1632,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503460</v>
+        <v>503258</v>
       </c>
       <c r="R9" t="n">
-        <v>7036014</v>
+        <v>7035950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1680,6 +1670,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1697,17 +1692,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131144288</v>
+        <v>131144278</v>
       </c>
       <c r="B10" t="n">
         <v>80355</v>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503258</v>
+        <v>503277</v>
       </c>
       <c r="R10" t="n">
-        <v>7035950</v>
+        <v>7035964</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131144269</v>
+        <v>131144259</v>
       </c>
       <c r="B34" t="n">
-        <v>80356</v>
+        <v>91818</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4872,26 +4872,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4899,10 +4903,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503190</v>
+        <v>503326</v>
       </c>
       <c r="R34" t="n">
-        <v>7035938</v>
+        <v>7035948</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4937,11 +4941,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4959,22 +4958,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4992,10 +4991,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131144259</v>
+        <v>131144269</v>
       </c>
       <c r="B35" t="n">
-        <v>91818</v>
+        <v>80356</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5003,30 +5002,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5034,10 +5029,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503326</v>
+        <v>503190</v>
       </c>
       <c r="R35" t="n">
-        <v>7035948</v>
+        <v>7035938</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5072,6 +5067,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5089,22 +5089,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131144264</v>
+        <v>131143996</v>
       </c>
       <c r="B36" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5133,29 +5133,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5165,10 +5164,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503447</v>
+        <v>503386</v>
       </c>
       <c r="R36" t="n">
-        <v>7035991</v>
+        <v>7036016</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5205,7 +5204,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5214,6 +5213,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5222,6 +5222,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
+        </is>
+      </c>
       <c r="AJ36" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5232,9 +5237,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5252,10 +5262,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131143967</v>
+        <v>131144294</v>
       </c>
       <c r="B37" t="n">
-        <v>57888</v>
+        <v>80355</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5263,31 +5273,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5295,10 +5300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503201</v>
+        <v>503563</v>
       </c>
       <c r="R37" t="n">
-        <v>7036058</v>
+        <v>7036044</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5335,7 +5340,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5344,6 +5349,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5352,29 +5358,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5392,10 +5393,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131143996</v>
+        <v>131144264</v>
       </c>
       <c r="B38" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5403,28 +5404,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5434,10 +5436,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503386</v>
+        <v>503447</v>
       </c>
       <c r="R38" t="n">
-        <v>7036016</v>
+        <v>7035991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5474,7 +5476,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5483,7 +5485,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5492,11 +5493,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
-        </is>
-      </c>
       <c r="AJ38" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5507,14 +5503,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5532,10 +5523,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131144294</v>
+        <v>131143967</v>
       </c>
       <c r="B39" t="n">
-        <v>80355</v>
+        <v>57888</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5543,26 +5534,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5570,10 +5566,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503563</v>
+        <v>503201</v>
       </c>
       <c r="R39" t="n">
-        <v>7036044</v>
+        <v>7036058</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5610,7 +5606,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5619,7 +5615,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5628,24 +5623,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -6699,10 +6699,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131144285</v>
+        <v>131144301</v>
       </c>
       <c r="B48" t="n">
-        <v>80355</v>
+        <v>91838</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6710,26 +6710,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503209</v>
+        <v>503583</v>
       </c>
       <c r="R48" t="n">
-        <v>7035903</v>
+        <v>7036073</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6775,11 +6775,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6797,22 +6792,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6830,7 +6820,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131143979</v>
+        <v>131144285</v>
       </c>
       <c r="B49" t="n">
         <v>80355</v>
@@ -6868,10 +6858,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503343</v>
+        <v>503209</v>
       </c>
       <c r="R49" t="n">
-        <v>7036013</v>
+        <v>7035903</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6904,6 +6894,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6956,10 +6951,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131144301</v>
+        <v>131143979</v>
       </c>
       <c r="B50" t="n">
-        <v>91838</v>
+        <v>80355</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6967,26 +6962,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6994,10 +6989,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503583</v>
+        <v>503343</v>
       </c>
       <c r="R50" t="n">
-        <v>7036073</v>
+        <v>7036013</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7049,17 +7044,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7077,32 +7077,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131143983</v>
+        <v>131144300</v>
       </c>
       <c r="B51" t="n">
-        <v>80355</v>
+        <v>80315</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503376</v>
+        <v>503318</v>
       </c>
       <c r="R51" t="n">
-        <v>7035991</v>
+        <v>7035950</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7151,6 +7151,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7203,32 +7208,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131144300</v>
+        <v>131143983</v>
       </c>
       <c r="B52" t="n">
-        <v>80315</v>
+        <v>80355</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7241,10 +7246,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503318</v>
+        <v>503376</v>
       </c>
       <c r="R52" t="n">
-        <v>7035950</v>
+        <v>7035991</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7277,11 +7282,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7717,10 +7717,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131144260</v>
+        <v>131143982</v>
       </c>
       <c r="B56" t="n">
-        <v>57888</v>
+        <v>80355</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7728,31 +7728,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7760,10 +7755,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503332</v>
+        <v>503364</v>
       </c>
       <c r="R56" t="n">
-        <v>7035948</v>
+        <v>7035989</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7798,17 +7793,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7819,22 +7810,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7852,10 +7843,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131144265</v>
+        <v>131143997</v>
       </c>
       <c r="B57" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7863,31 +7854,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7895,10 +7881,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503516</v>
+        <v>503416</v>
       </c>
       <c r="R57" t="n">
-        <v>7036022</v>
+        <v>7036029</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7933,17 +7919,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7982,7 +7964,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131143982</v>
+        <v>131144280</v>
       </c>
       <c r="B58" t="n">
         <v>80355</v>
@@ -8020,10 +8002,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503364</v>
+        <v>503251</v>
       </c>
       <c r="R58" t="n">
-        <v>7035989</v>
+        <v>7035966</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8056,6 +8038,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8108,10 +8095,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131143997</v>
+        <v>131144275</v>
       </c>
       <c r="B59" t="n">
-        <v>79250</v>
+        <v>80355</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8119,21 +8106,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8146,10 +8133,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503416</v>
+        <v>503195</v>
       </c>
       <c r="R59" t="n">
-        <v>7036029</v>
+        <v>7036062</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8184,6 +8171,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -8201,17 +8193,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8229,7 +8226,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131144280</v>
+        <v>131144291</v>
       </c>
       <c r="B60" t="n">
         <v>80355</v>
@@ -8267,10 +8264,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503251</v>
+        <v>503317</v>
       </c>
       <c r="R60" t="n">
-        <v>7035966</v>
+        <v>7035948</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8360,10 +8357,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131144275</v>
+        <v>131143991</v>
       </c>
       <c r="B61" t="n">
-        <v>80355</v>
+        <v>79250</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8371,21 +8368,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8398,10 +8395,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503195</v>
+        <v>503400</v>
       </c>
       <c r="R61" t="n">
-        <v>7036062</v>
+        <v>7036159</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8436,11 +8433,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8458,22 +8450,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8491,7 +8478,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131144291</v>
+        <v>131144297</v>
       </c>
       <c r="B62" t="n">
         <v>80355</v>
@@ -8529,10 +8516,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503317</v>
+        <v>503354</v>
       </c>
       <c r="R62" t="n">
-        <v>7035948</v>
+        <v>7036143</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8622,7 +8609,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131143991</v>
+        <v>131143995</v>
       </c>
       <c r="B63" t="n">
         <v>79250</v>
@@ -8660,10 +8647,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503400</v>
+        <v>503216</v>
       </c>
       <c r="R63" t="n">
-        <v>7036159</v>
+        <v>7036078</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8743,10 +8730,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131144297</v>
+        <v>131144260</v>
       </c>
       <c r="B64" t="n">
-        <v>80355</v>
+        <v>57888</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8754,26 +8741,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8781,10 +8773,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503354</v>
+        <v>503332</v>
       </c>
       <c r="R64" t="n">
-        <v>7036143</v>
+        <v>7035948</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8821,7 +8813,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8830,7 +8822,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8841,22 +8832,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8874,10 +8865,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131143995</v>
+        <v>131144265</v>
       </c>
       <c r="B65" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8885,26 +8876,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8912,10 +8908,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503216</v>
+        <v>503516</v>
       </c>
       <c r="R65" t="n">
-        <v>7036078</v>
+        <v>7036022</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8950,13 +8946,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -9265,10 +9265,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131144283</v>
+        <v>131144001</v>
       </c>
       <c r="B68" t="n">
-        <v>80355</v>
+        <v>79250</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9276,21 +9276,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503196</v>
+        <v>503574</v>
       </c>
       <c r="R68" t="n">
-        <v>7035909</v>
+        <v>7036113</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9341,11 +9341,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9363,22 +9358,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9396,10 +9386,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131144001</v>
+        <v>131144298</v>
       </c>
       <c r="B69" t="n">
-        <v>79250</v>
+        <v>80355</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9407,21 +9397,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9434,10 +9424,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503574</v>
+        <v>503191</v>
       </c>
       <c r="R69" t="n">
-        <v>7036113</v>
+        <v>7035913</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9472,6 +9462,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9489,17 +9484,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9517,32 +9517,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131143974</v>
+        <v>131144283</v>
       </c>
       <c r="B70" t="n">
-        <v>80384</v>
+        <v>80355</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503424</v>
+        <v>503196</v>
       </c>
       <c r="R70" t="n">
-        <v>7036001</v>
+        <v>7035909</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9648,32 +9648,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131144298</v>
+        <v>131143974</v>
       </c>
       <c r="B71" t="n">
-        <v>80355</v>
+        <v>80384</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503191</v>
+        <v>503424</v>
       </c>
       <c r="R71" t="n">
-        <v>7035913</v>
+        <v>7036001</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9909,10 +9909,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131144289</v>
+        <v>131144261</v>
       </c>
       <c r="B73" t="n">
-        <v>80355</v>
+        <v>57888</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9920,26 +9920,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9947,10 +9952,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503258</v>
+        <v>503332</v>
       </c>
       <c r="R73" t="n">
-        <v>7035952</v>
+        <v>7035950</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9987,7 +9992,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9996,7 +10001,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -10007,22 +10011,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10040,10 +10044,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131144261</v>
+        <v>131144289</v>
       </c>
       <c r="B74" t="n">
-        <v>57888</v>
+        <v>80355</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10051,31 +10055,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10083,10 +10082,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503332</v>
+        <v>503258</v>
       </c>
       <c r="R74" t="n">
-        <v>7035950</v>
+        <v>7035952</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10123,7 +10122,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10132,6 +10131,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>

--- a/artfynd/A 379-2026 artfynd.xlsx
+++ b/artfynd/A 379-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131144266</v>
+        <v>131143977</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>80355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503547</v>
+        <v>503254</v>
       </c>
       <c r="R2" t="n">
-        <v>7036037</v>
+        <v>7036092</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,22 +777,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,39 +810,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131143977</v>
+        <v>131143975</v>
       </c>
       <c r="B3" t="n">
-        <v>80355</v>
+        <v>80384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503254</v>
+        <v>503441</v>
       </c>
       <c r="R3" t="n">
-        <v>7036092</v>
+        <v>7036004</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131143975</v>
+        <v>131143973</v>
       </c>
       <c r="B4" t="n">
         <v>80384</v>
@@ -975,11 +975,7 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -987,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503441</v>
+        <v>503418</v>
       </c>
       <c r="R4" t="n">
-        <v>7036004</v>
+        <v>7036017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1080,37 +1076,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131143973</v>
+        <v>131144266</v>
       </c>
       <c r="B5" t="n">
-        <v>80384</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1118,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503418</v>
+        <v>503547</v>
       </c>
       <c r="R5" t="n">
-        <v>7036017</v>
+        <v>7036037</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1158,7 +1159,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,7 +1168,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1178,22 +1178,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131144259</v>
+        <v>131144269</v>
       </c>
       <c r="B34" t="n">
-        <v>91818</v>
+        <v>80356</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4872,30 +4872,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4903,10 +4899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503326</v>
+        <v>503190</v>
       </c>
       <c r="R34" t="n">
-        <v>7035948</v>
+        <v>7035938</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4941,6 +4937,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4958,22 +4959,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4991,10 +4992,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131144269</v>
+        <v>131143996</v>
       </c>
       <c r="B35" t="n">
-        <v>80356</v>
+        <v>79250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5002,26 +5003,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5029,10 +5034,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503190</v>
+        <v>503386</v>
       </c>
       <c r="R35" t="n">
-        <v>7035938</v>
+        <v>7036016</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5069,7 +5074,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5087,24 +5092,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
+        </is>
+      </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5122,10 +5132,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131143996</v>
+        <v>131144294</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>80355</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5133,30 +5143,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5164,10 +5170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503386</v>
+        <v>503563</v>
       </c>
       <c r="R36" t="n">
-        <v>7036016</v>
+        <v>7036044</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5204,7 +5210,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5222,29 +5228,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
-        </is>
-      </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5262,10 +5263,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131144294</v>
+        <v>131144259</v>
       </c>
       <c r="B37" t="n">
-        <v>80355</v>
+        <v>91818</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5273,26 +5274,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5300,10 +5305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503563</v>
+        <v>503326</v>
       </c>
       <c r="R37" t="n">
-        <v>7036044</v>
+        <v>7035948</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5338,11 +5343,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5360,22 +5360,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -7717,10 +7717,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131143982</v>
+        <v>131144260</v>
       </c>
       <c r="B56" t="n">
-        <v>80355</v>
+        <v>57888</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7728,26 +7728,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7755,10 +7760,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503364</v>
+        <v>503332</v>
       </c>
       <c r="R56" t="n">
-        <v>7035989</v>
+        <v>7035948</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7793,13 +7798,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7810,22 +7819,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7843,10 +7852,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131143997</v>
+        <v>131144265</v>
       </c>
       <c r="B57" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7854,26 +7863,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7881,10 +7895,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503416</v>
+        <v>503516</v>
       </c>
       <c r="R57" t="n">
-        <v>7036029</v>
+        <v>7036022</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7919,13 +7933,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7964,7 +7982,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131144280</v>
+        <v>131143982</v>
       </c>
       <c r="B58" t="n">
         <v>80355</v>
@@ -8002,10 +8020,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503251</v>
+        <v>503364</v>
       </c>
       <c r="R58" t="n">
-        <v>7035966</v>
+        <v>7035989</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8038,11 +8056,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8095,10 +8108,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131144275</v>
+        <v>131143997</v>
       </c>
       <c r="B59" t="n">
-        <v>80355</v>
+        <v>79250</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8106,21 +8119,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8133,10 +8146,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503195</v>
+        <v>503416</v>
       </c>
       <c r="R59" t="n">
-        <v>7036062</v>
+        <v>7036029</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8171,11 +8184,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -8193,22 +8201,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8226,7 +8229,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131144291</v>
+        <v>131144280</v>
       </c>
       <c r="B60" t="n">
         <v>80355</v>
@@ -8264,10 +8267,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503317</v>
+        <v>503251</v>
       </c>
       <c r="R60" t="n">
-        <v>7035948</v>
+        <v>7035966</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8357,10 +8360,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131143991</v>
+        <v>131144275</v>
       </c>
       <c r="B61" t="n">
-        <v>79250</v>
+        <v>80355</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8368,21 +8371,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8395,10 +8398,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503400</v>
+        <v>503195</v>
       </c>
       <c r="R61" t="n">
-        <v>7036159</v>
+        <v>7036062</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8433,6 +8436,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8450,17 +8458,22 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8478,7 +8491,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131144297</v>
+        <v>131144291</v>
       </c>
       <c r="B62" t="n">
         <v>80355</v>
@@ -8516,10 +8529,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503354</v>
+        <v>503317</v>
       </c>
       <c r="R62" t="n">
-        <v>7036143</v>
+        <v>7035948</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8609,7 +8622,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131143995</v>
+        <v>131143991</v>
       </c>
       <c r="B63" t="n">
         <v>79250</v>
@@ -8647,10 +8660,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503216</v>
+        <v>503400</v>
       </c>
       <c r="R63" t="n">
-        <v>7036078</v>
+        <v>7036159</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8730,10 +8743,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131144260</v>
+        <v>131144297</v>
       </c>
       <c r="B64" t="n">
-        <v>57888</v>
+        <v>80355</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8741,31 +8754,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8773,10 +8781,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503332</v>
+        <v>503354</v>
       </c>
       <c r="R64" t="n">
-        <v>7035948</v>
+        <v>7036143</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8813,7 +8821,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8822,6 +8830,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8832,22 +8841,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8865,10 +8874,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131144265</v>
+        <v>131143995</v>
       </c>
       <c r="B65" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8876,31 +8885,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8908,10 +8912,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503516</v>
+        <v>503216</v>
       </c>
       <c r="R65" t="n">
-        <v>7036022</v>
+        <v>7036078</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8946,17 +8950,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 379-2026 artfynd.xlsx
+++ b/artfynd/A 379-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131143977</v>
       </c>
       <c r="B2" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131143975</v>
       </c>
       <c r="B3" t="n">
-        <v>80384</v>
+        <v>80387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131143973</v>
       </c>
       <c r="B4" t="n">
-        <v>80384</v>
+        <v>80387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>131144266</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>131143999</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>131143978</v>
       </c>
       <c r="B7" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>131144271</v>
       </c>
       <c r="B8" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>131144288</v>
       </c>
       <c r="B9" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>131144278</v>
       </c>
       <c r="B10" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>131143990</v>
       </c>
       <c r="B11" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>131144287</v>
       </c>
       <c r="B12" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>131144272</v>
       </c>
       <c r="B13" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>131143987</v>
       </c>
       <c r="B14" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>131144279</v>
       </c>
       <c r="B15" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>131144296</v>
       </c>
       <c r="B16" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>131143980</v>
       </c>
       <c r="B17" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>131144292</v>
       </c>
       <c r="B18" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131143984</v>
       </c>
       <c r="B19" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>131144274</v>
       </c>
       <c r="B20" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>131143986</v>
       </c>
       <c r="B21" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3310,41 +3310,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131143972</v>
+        <v>131143998</v>
       </c>
       <c r="B22" t="n">
-        <v>80384</v>
+        <v>79253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3352,10 +3348,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503377</v>
+        <v>503444</v>
       </c>
       <c r="R22" t="n">
-        <v>7036016</v>
+        <v>7036006</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3392,7 +3388,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3412,22 +3408,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3445,37 +3436,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131143976</v>
+        <v>131143972</v>
       </c>
       <c r="B23" t="n">
-        <v>80355</v>
+        <v>80387</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3483,10 +3478,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503419</v>
+        <v>503377</v>
       </c>
       <c r="R23" t="n">
-        <v>7036154</v>
+        <v>7036016</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3519,6 +3514,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131143989</v>
+        <v>131143976</v>
       </c>
       <c r="B24" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503448</v>
+        <v>503419</v>
       </c>
       <c r="R24" t="n">
-        <v>7036030</v>
+        <v>7036154</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3647,11 +3647,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Lunglav på en gran vid en rönn med lunglav.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3669,22 +3664,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3702,10 +3697,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131143998</v>
+        <v>131143989</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>80358</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3713,21 +3708,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3740,10 +3735,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503444</v>
+        <v>503448</v>
       </c>
       <c r="R25" t="n">
-        <v>7036006</v>
+        <v>7036030</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3780,7 +3775,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Lunglav på en gran vid en rönn med lunglav.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3808,9 +3803,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
         <v>131144299</v>
       </c>
       <c r="B26" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>131144290</v>
       </c>
       <c r="B27" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>131144284</v>
       </c>
       <c r="B28" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>131143988</v>
       </c>
       <c r="B29" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>131143993</v>
       </c>
       <c r="B30" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131144281</v>
+        <v>131143994</v>
       </c>
       <c r="B31" t="n">
-        <v>80355</v>
+        <v>79253</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503194</v>
+        <v>503252</v>
       </c>
       <c r="R31" t="n">
-        <v>7035963</v>
+        <v>7036082</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4571,22 +4571,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4604,10 +4599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131143994</v>
+        <v>131144281</v>
       </c>
       <c r="B32" t="n">
-        <v>79250</v>
+        <v>80358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4615,21 +4610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4642,10 +4637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503252</v>
+        <v>503194</v>
       </c>
       <c r="R32" t="n">
-        <v>7036082</v>
+        <v>7035963</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4682,7 +4677,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4702,17 +4697,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4733,7 +4733,7 @@
         <v>131144293</v>
       </c>
       <c r="B33" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131144269</v>
+        <v>131143996</v>
       </c>
       <c r="B34" t="n">
-        <v>80356</v>
+        <v>79253</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4872,26 +4872,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4899,10 +4903,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503190</v>
+        <v>503386</v>
       </c>
       <c r="R34" t="n">
-        <v>7035938</v>
+        <v>7036016</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4939,7 +4943,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4957,24 +4961,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
+        </is>
+      </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4992,10 +5001,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131143996</v>
+        <v>131144294</v>
       </c>
       <c r="B35" t="n">
-        <v>79250</v>
+        <v>80358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5003,30 +5012,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5034,10 +5039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503386</v>
+        <v>503563</v>
       </c>
       <c r="R35" t="n">
-        <v>7036016</v>
+        <v>7036044</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5074,7 +5079,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5092,29 +5097,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
-        </is>
-      </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5132,10 +5132,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131144294</v>
+        <v>131144264</v>
       </c>
       <c r="B36" t="n">
-        <v>80355</v>
+        <v>57891</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5143,26 +5143,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5170,10 +5175,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503563</v>
+        <v>503447</v>
       </c>
       <c r="R36" t="n">
-        <v>7036044</v>
+        <v>7035991</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5210,7 +5215,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5219,7 +5224,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5230,22 +5234,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5263,10 +5262,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131144259</v>
+        <v>131143967</v>
       </c>
       <c r="B37" t="n">
-        <v>91818</v>
+        <v>57891</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5274,28 +5273,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503326</v>
+        <v>503201</v>
       </c>
       <c r="R37" t="n">
-        <v>7035948</v>
+        <v>7036058</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5343,13 +5343,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5358,6 +5362,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ37" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5370,12 +5379,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5393,10 +5402,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131144264</v>
+        <v>131144269</v>
       </c>
       <c r="B38" t="n">
-        <v>57888</v>
+        <v>80359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5404,31 +5413,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5436,10 +5440,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503447</v>
+        <v>503190</v>
       </c>
       <c r="R38" t="n">
-        <v>7035991</v>
+        <v>7035938</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5476,7 +5480,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5485,6 +5489,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5495,17 +5500,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5523,10 +5533,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131143967</v>
+        <v>131144259</v>
       </c>
       <c r="B39" t="n">
-        <v>57888</v>
+        <v>91821</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5534,29 +5544,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5566,10 +5575,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503201</v>
+        <v>503326</v>
       </c>
       <c r="R39" t="n">
-        <v>7036058</v>
+        <v>7035948</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5604,17 +5613,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5623,11 +5628,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ39" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5666,7 +5666,7 @@
         <v>131143992</v>
       </c>
       <c r="B40" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>131144270</v>
       </c>
       <c r="B41" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>131144282</v>
       </c>
       <c r="B42" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>131144276</v>
       </c>
       <c r="B43" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>131144267</v>
       </c>
       <c r="B44" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>131144263</v>
       </c>
       <c r="B45" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>131144295</v>
       </c>
       <c r="B46" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>131143981</v>
       </c>
       <c r="B47" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>131144301</v>
       </c>
       <c r="B48" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>131144285</v>
       </c>
       <c r="B49" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>131143979</v>
       </c>
       <c r="B50" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>131144300</v>
       </c>
       <c r="B51" t="n">
-        <v>80315</v>
+        <v>80318</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>131143983</v>
       </c>
       <c r="B52" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>131144000</v>
       </c>
       <c r="B53" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>131144286</v>
       </c>
       <c r="B54" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>131144277</v>
       </c>
       <c r="B55" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7717,10 +7717,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131144260</v>
+        <v>131143997</v>
       </c>
       <c r="B56" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7728,31 +7728,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7760,10 +7755,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503332</v>
+        <v>503416</v>
       </c>
       <c r="R56" t="n">
-        <v>7035948</v>
+        <v>7036029</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7798,17 +7793,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7827,14 +7818,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7852,10 +7838,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131144265</v>
+        <v>131143991</v>
       </c>
       <c r="B57" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7863,31 +7849,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7895,10 +7876,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503516</v>
+        <v>503400</v>
       </c>
       <c r="R57" t="n">
-        <v>7036022</v>
+        <v>7036159</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7933,17 +7914,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7982,10 +7959,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131143982</v>
+        <v>131143995</v>
       </c>
       <c r="B58" t="n">
-        <v>80355</v>
+        <v>79253</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7993,21 +7970,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8020,10 +7997,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503364</v>
+        <v>503216</v>
       </c>
       <c r="R58" t="n">
-        <v>7035989</v>
+        <v>7036078</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8075,22 +8052,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8108,10 +8080,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131143997</v>
+        <v>131143982</v>
       </c>
       <c r="B59" t="n">
-        <v>79250</v>
+        <v>80358</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8119,21 +8091,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8146,10 +8118,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503416</v>
+        <v>503364</v>
       </c>
       <c r="R59" t="n">
-        <v>7036029</v>
+        <v>7035989</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8201,17 +8173,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8232,7 +8209,7 @@
         <v>131144280</v>
       </c>
       <c r="B60" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8363,7 +8340,7 @@
         <v>131144275</v>
       </c>
       <c r="B61" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8494,7 +8471,7 @@
         <v>131144291</v>
       </c>
       <c r="B62" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8622,10 +8599,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131143991</v>
+        <v>131144297</v>
       </c>
       <c r="B63" t="n">
-        <v>79250</v>
+        <v>80358</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8633,21 +8610,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8660,10 +8637,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503400</v>
+        <v>503354</v>
       </c>
       <c r="R63" t="n">
-        <v>7036159</v>
+        <v>7036143</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8698,6 +8675,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8715,17 +8697,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8743,10 +8730,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131144297</v>
+        <v>131144260</v>
       </c>
       <c r="B64" t="n">
-        <v>80355</v>
+        <v>57891</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8754,26 +8741,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8781,10 +8773,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503354</v>
+        <v>503332</v>
       </c>
       <c r="R64" t="n">
-        <v>7036143</v>
+        <v>7035948</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8821,7 +8813,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8830,7 +8822,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8841,22 +8832,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8874,10 +8865,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131143995</v>
+        <v>131144265</v>
       </c>
       <c r="B65" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8885,26 +8876,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8912,10 +8908,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503216</v>
+        <v>503516</v>
       </c>
       <c r="R65" t="n">
-        <v>7036078</v>
+        <v>7036022</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8950,13 +8946,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8998,7 +8998,7 @@
         <v>131144268</v>
       </c>
       <c r="B66" t="n">
-        <v>80384</v>
+        <v>80387</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>131143968</v>
       </c>
       <c r="B67" t="n">
-        <v>80384</v>
+        <v>80387</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9265,10 +9265,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131144001</v>
+        <v>131144283</v>
       </c>
       <c r="B68" t="n">
-        <v>79250</v>
+        <v>80358</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9276,21 +9276,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503574</v>
+        <v>503196</v>
       </c>
       <c r="R68" t="n">
-        <v>7036113</v>
+        <v>7035909</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9341,6 +9341,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9358,17 +9363,22 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9386,10 +9396,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131144298</v>
+        <v>131144001</v>
       </c>
       <c r="B69" t="n">
-        <v>80355</v>
+        <v>79253</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9397,21 +9407,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9424,10 +9434,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503191</v>
+        <v>503574</v>
       </c>
       <c r="R69" t="n">
-        <v>7035913</v>
+        <v>7036113</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9462,11 +9472,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9484,22 +9489,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9517,32 +9517,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131144283</v>
+        <v>131143974</v>
       </c>
       <c r="B70" t="n">
-        <v>80355</v>
+        <v>80387</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503196</v>
+        <v>503424</v>
       </c>
       <c r="R70" t="n">
-        <v>7035909</v>
+        <v>7036001</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9648,32 +9648,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131143974</v>
+        <v>131144298</v>
       </c>
       <c r="B71" t="n">
-        <v>80384</v>
+        <v>80358</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503424</v>
+        <v>503191</v>
       </c>
       <c r="R71" t="n">
-        <v>7036001</v>
+        <v>7035913</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9782,7 +9782,7 @@
         <v>131144262</v>
       </c>
       <c r="B72" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9909,10 +9909,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131144261</v>
+        <v>131144289</v>
       </c>
       <c r="B73" t="n">
-        <v>57888</v>
+        <v>80358</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9920,31 +9920,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9952,10 +9947,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503332</v>
+        <v>503258</v>
       </c>
       <c r="R73" t="n">
-        <v>7035950</v>
+        <v>7035952</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9992,7 +9987,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10001,6 +9996,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -10011,22 +10007,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10044,10 +10040,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131144289</v>
+        <v>131144261</v>
       </c>
       <c r="B74" t="n">
-        <v>80355</v>
+        <v>57891</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10055,26 +10051,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10082,10 +10083,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503258</v>
+        <v>503332</v>
       </c>
       <c r="R74" t="n">
-        <v>7035952</v>
+        <v>7035950</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10122,7 +10123,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10131,7 +10132,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10175,41 +10175,37 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131143970</v>
+        <v>131144302</v>
       </c>
       <c r="B75" t="n">
-        <v>80384</v>
+        <v>79253</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10217,10 +10213,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503376</v>
+        <v>503606</v>
       </c>
       <c r="R75" t="n">
-        <v>7035991</v>
+        <v>7036064</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10272,22 +10268,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10305,37 +10296,41 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131144302</v>
+        <v>131143970</v>
       </c>
       <c r="B76" t="n">
-        <v>79250</v>
+        <v>80387</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10343,10 +10338,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503606</v>
+        <v>503376</v>
       </c>
       <c r="R76" t="n">
-        <v>7036064</v>
+        <v>7035991</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10398,17 +10393,22 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10429,7 +10429,7 @@
         <v>131144273</v>
       </c>
       <c r="B77" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 379-2026 artfynd.xlsx
+++ b/artfynd/A 379-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131143977</v>
       </c>
       <c r="B2" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131143975</v>
       </c>
       <c r="B3" t="n">
-        <v>80387</v>
+        <v>80388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131143973</v>
       </c>
       <c r="B4" t="n">
-        <v>80387</v>
+        <v>80388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>131144266</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>131143999</v>
       </c>
       <c r="B6" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>131143978</v>
       </c>
       <c r="B7" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>131144271</v>
       </c>
       <c r="B8" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>131144288</v>
       </c>
       <c r="B9" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>131144278</v>
       </c>
       <c r="B10" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>131143990</v>
       </c>
       <c r="B11" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>131144287</v>
       </c>
       <c r="B12" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>131144272</v>
       </c>
       <c r="B13" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>131143987</v>
       </c>
       <c r="B14" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>131144279</v>
       </c>
       <c r="B15" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>131144296</v>
       </c>
       <c r="B16" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>131143980</v>
       </c>
       <c r="B17" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>131144292</v>
       </c>
       <c r="B18" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131143984</v>
       </c>
       <c r="B19" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>131144274</v>
       </c>
       <c r="B20" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>131143986</v>
       </c>
       <c r="B21" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>131143998</v>
       </c>
       <c r="B22" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>131143972</v>
       </c>
       <c r="B23" t="n">
-        <v>80387</v>
+        <v>80388</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>131143976</v>
       </c>
       <c r="B24" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>131143989</v>
       </c>
       <c r="B25" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>131144299</v>
       </c>
       <c r="B26" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>131144290</v>
       </c>
       <c r="B27" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>131144284</v>
       </c>
       <c r="B28" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>131143988</v>
       </c>
       <c r="B29" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>131143993</v>
       </c>
       <c r="B30" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>131143994</v>
       </c>
       <c r="B31" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>131144281</v>
       </c>
       <c r="B32" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>131144293</v>
       </c>
       <c r="B33" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131143996</v>
+        <v>131144259</v>
       </c>
       <c r="B34" t="n">
-        <v>79253</v>
+        <v>91822</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4872,28 +4872,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503386</v>
+        <v>503326</v>
       </c>
       <c r="R34" t="n">
-        <v>7036016</v>
+        <v>7035948</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4941,11 +4941,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4961,11 +4956,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
-        </is>
-      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4978,12 +4968,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5001,10 +4991,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131144294</v>
+        <v>131144269</v>
       </c>
       <c r="B35" t="n">
-        <v>80358</v>
+        <v>80360</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5012,21 +5002,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5039,10 +5029,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503563</v>
+        <v>503190</v>
       </c>
       <c r="R35" t="n">
-        <v>7036044</v>
+        <v>7035938</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5132,10 +5122,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131144264</v>
+        <v>131144294</v>
       </c>
       <c r="B36" t="n">
-        <v>57891</v>
+        <v>80359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5143,31 +5133,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5175,10 +5160,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503447</v>
+        <v>503563</v>
       </c>
       <c r="R36" t="n">
-        <v>7035991</v>
+        <v>7036044</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5215,7 +5200,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5224,6 +5209,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5234,17 +5220,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5262,10 +5253,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131143967</v>
+        <v>131144264</v>
       </c>
       <c r="B37" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5295,7 +5286,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5305,10 +5296,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503201</v>
+        <v>503447</v>
       </c>
       <c r="R37" t="n">
-        <v>7036058</v>
+        <v>7035991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5345,7 +5336,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5362,11 +5353,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ37" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5377,14 +5363,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5402,10 +5383,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131144269</v>
+        <v>131143967</v>
       </c>
       <c r="B38" t="n">
-        <v>80359</v>
+        <v>57892</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5413,26 +5394,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5440,10 +5426,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503190</v>
+        <v>503201</v>
       </c>
       <c r="R38" t="n">
-        <v>7035938</v>
+        <v>7036058</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5480,7 +5466,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5489,7 +5475,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5498,24 +5483,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5533,10 +5523,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131144259</v>
+        <v>131143996</v>
       </c>
       <c r="B39" t="n">
-        <v>91821</v>
+        <v>79254</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5544,28 +5534,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5575,10 +5565,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503326</v>
+        <v>503386</v>
       </c>
       <c r="R39" t="n">
-        <v>7035948</v>
+        <v>7036016</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5613,6 +5603,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5628,6 +5623,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
+        </is>
+      </c>
       <c r="AJ39" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5666,7 +5666,7 @@
         <v>131143992</v>
       </c>
       <c r="B40" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5784,10 +5784,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131144270</v>
+        <v>131144267</v>
       </c>
       <c r="B41" t="n">
-        <v>80358</v>
+        <v>57892</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5795,26 +5795,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5822,10 +5827,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503423</v>
+        <v>503564</v>
       </c>
       <c r="R41" t="n">
-        <v>7036145</v>
+        <v>7036045</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5862,7 +5867,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5871,7 +5876,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5882,22 +5886,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5915,10 +5914,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131144282</v>
+        <v>131144263</v>
       </c>
       <c r="B42" t="n">
-        <v>80358</v>
+        <v>57892</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5926,26 +5925,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5953,10 +5957,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503179</v>
+        <v>503363</v>
       </c>
       <c r="R42" t="n">
-        <v>7035940</v>
+        <v>7035960</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5993,7 +5997,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6002,7 +6006,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6013,22 +6016,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6046,10 +6049,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131144276</v>
+        <v>131144270</v>
       </c>
       <c r="B43" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6084,10 +6087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503155</v>
+        <v>503423</v>
       </c>
       <c r="R43" t="n">
-        <v>7035984</v>
+        <v>7036145</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6177,10 +6180,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131144267</v>
+        <v>131144282</v>
       </c>
       <c r="B44" t="n">
-        <v>57891</v>
+        <v>80359</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6188,31 +6191,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6220,10 +6218,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503564</v>
+        <v>503179</v>
       </c>
       <c r="R44" t="n">
-        <v>7036045</v>
+        <v>7035940</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6260,7 +6258,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6269,6 +6267,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6279,17 +6278,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6307,10 +6311,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131144263</v>
+        <v>131144276</v>
       </c>
       <c r="B45" t="n">
-        <v>57891</v>
+        <v>80359</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6318,31 +6322,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6350,10 +6349,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503363</v>
+        <v>503155</v>
       </c>
       <c r="R45" t="n">
-        <v>7035960</v>
+        <v>7035984</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6390,7 +6389,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6399,6 +6398,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6409,22 +6409,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6445,7 +6445,7 @@
         <v>131144295</v>
       </c>
       <c r="B46" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>131143981</v>
       </c>
       <c r="B47" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>131144301</v>
       </c>
       <c r="B48" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>131144285</v>
       </c>
       <c r="B49" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>131143979</v>
       </c>
       <c r="B50" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7077,32 +7077,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131144300</v>
+        <v>131143983</v>
       </c>
       <c r="B51" t="n">
-        <v>80318</v>
+        <v>80359</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503318</v>
+        <v>503376</v>
       </c>
       <c r="R51" t="n">
-        <v>7035950</v>
+        <v>7035991</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7151,11 +7151,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7208,32 +7203,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131143983</v>
+        <v>131144300</v>
       </c>
       <c r="B52" t="n">
-        <v>80358</v>
+        <v>80319</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7246,10 +7241,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503376</v>
+        <v>503318</v>
       </c>
       <c r="R52" t="n">
-        <v>7035991</v>
+        <v>7035950</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7282,6 +7277,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7337,7 +7337,7 @@
         <v>131144000</v>
       </c>
       <c r="B53" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>131144286</v>
       </c>
       <c r="B54" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>131144277</v>
       </c>
       <c r="B55" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>131143997</v>
       </c>
       <c r="B56" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>131143991</v>
       </c>
       <c r="B57" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>131143995</v>
       </c>
       <c r="B58" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>131143982</v>
       </c>
       <c r="B59" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>131144280</v>
       </c>
       <c r="B60" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>131144275</v>
       </c>
       <c r="B61" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>131144291</v>
       </c>
       <c r="B62" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>131144297</v>
       </c>
       <c r="B63" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>131144260</v>
       </c>
       <c r="B64" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>131144265</v>
       </c>
       <c r="B65" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8995,41 +8995,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131144268</v>
+        <v>131144001</v>
       </c>
       <c r="B66" t="n">
-        <v>80387</v>
+        <v>79254</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9037,10 +9033,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503554</v>
+        <v>503574</v>
       </c>
       <c r="R66" t="n">
-        <v>7036090</v>
+        <v>7036113</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9075,11 +9071,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9097,22 +9088,17 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9130,10 +9116,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131143968</v>
+        <v>131144268</v>
       </c>
       <c r="B67" t="n">
-        <v>80387</v>
+        <v>80388</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9172,10 +9158,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503216</v>
+        <v>503554</v>
       </c>
       <c r="R67" t="n">
-        <v>7036102</v>
+        <v>7036090</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9265,37 +9251,41 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131144283</v>
+        <v>131143968</v>
       </c>
       <c r="B68" t="n">
-        <v>80358</v>
+        <v>80388</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9303,10 +9293,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503196</v>
+        <v>503216</v>
       </c>
       <c r="R68" t="n">
-        <v>7035909</v>
+        <v>7036102</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9396,10 +9386,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131144001</v>
+        <v>131144283</v>
       </c>
       <c r="B69" t="n">
-        <v>79253</v>
+        <v>80359</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9407,21 +9397,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9434,10 +9424,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503574</v>
+        <v>503196</v>
       </c>
       <c r="R69" t="n">
-        <v>7036113</v>
+        <v>7035909</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9472,6 +9462,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9489,17 +9484,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9520,7 +9520,7 @@
         <v>131143974</v>
       </c>
       <c r="B70" t="n">
-        <v>80387</v>
+        <v>80388</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>131144298</v>
       </c>
       <c r="B71" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>131144262</v>
       </c>
       <c r="B72" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>131144289</v>
       </c>
       <c r="B73" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>131144261</v>
       </c>
       <c r="B74" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10175,37 +10175,41 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131144302</v>
+        <v>131143970</v>
       </c>
       <c r="B75" t="n">
-        <v>79253</v>
+        <v>80388</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10213,10 +10217,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503606</v>
+        <v>503376</v>
       </c>
       <c r="R75" t="n">
-        <v>7036064</v>
+        <v>7035991</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10268,17 +10272,22 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10296,41 +10305,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131143970</v>
+        <v>131144273</v>
       </c>
       <c r="B76" t="n">
-        <v>80387</v>
+        <v>80359</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10338,10 +10343,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503376</v>
+        <v>503267</v>
       </c>
       <c r="R76" t="n">
-        <v>7035991</v>
+        <v>7036145</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10374,6 +10379,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10426,10 +10436,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131144273</v>
+        <v>131144302</v>
       </c>
       <c r="B77" t="n">
-        <v>80358</v>
+        <v>79254</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10437,21 +10447,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10464,10 +10474,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503267</v>
+        <v>503606</v>
       </c>
       <c r="R77" t="n">
-        <v>7036145</v>
+        <v>7036064</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10502,11 +10512,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10524,22 +10529,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>

--- a/artfynd/A 379-2026 artfynd.xlsx
+++ b/artfynd/A 379-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131143977</v>
+        <v>131144266</v>
       </c>
       <c r="B2" t="n">
-        <v>80359</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503254</v>
+        <v>503547</v>
       </c>
       <c r="R2" t="n">
-        <v>7036092</v>
+        <v>7036037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,22 +777,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,39 +810,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131143975</v>
+        <v>131143977</v>
       </c>
       <c r="B3" t="n">
-        <v>80388</v>
+        <v>80359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503441</v>
+        <v>503254</v>
       </c>
       <c r="R3" t="n">
-        <v>7036004</v>
+        <v>7036092</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131143973</v>
+        <v>131143975</v>
       </c>
       <c r="B4" t="n">
         <v>80388</v>
@@ -975,7 +975,11 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503418</v>
+        <v>503441</v>
       </c>
       <c r="R4" t="n">
-        <v>7036017</v>
+        <v>7036004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1076,42 +1080,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131144266</v>
+        <v>131143973</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>80388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1119,10 +1118,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503547</v>
+        <v>503418</v>
       </c>
       <c r="R5" t="n">
-        <v>7036037</v>
+        <v>7036017</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1158,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,6 +1167,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1178,22 +1178,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131144259</v>
+        <v>131143996</v>
       </c>
       <c r="B34" t="n">
-        <v>91822</v>
+        <v>79254</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4872,28 +4872,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503326</v>
+        <v>503386</v>
       </c>
       <c r="R34" t="n">
-        <v>7035948</v>
+        <v>7036016</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4941,6 +4941,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4956,6 +4961,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
+        </is>
+      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4968,12 +4978,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4991,10 +5001,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131144269</v>
+        <v>131144259</v>
       </c>
       <c r="B35" t="n">
-        <v>80360</v>
+        <v>91822</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5002,26 +5012,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5029,10 +5043,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503190</v>
+        <v>503326</v>
       </c>
       <c r="R35" t="n">
-        <v>7035938</v>
+        <v>7035948</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5067,11 +5081,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5089,22 +5098,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5122,10 +5131,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131144294</v>
+        <v>131144269</v>
       </c>
       <c r="B36" t="n">
-        <v>80359</v>
+        <v>80360</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5133,21 +5142,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5160,10 +5169,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503563</v>
+        <v>503190</v>
       </c>
       <c r="R36" t="n">
-        <v>7036044</v>
+        <v>7035938</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5253,10 +5262,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131144264</v>
+        <v>131144294</v>
       </c>
       <c r="B37" t="n">
-        <v>57892</v>
+        <v>80359</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5264,31 +5273,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5296,10 +5300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503447</v>
+        <v>503563</v>
       </c>
       <c r="R37" t="n">
-        <v>7035991</v>
+        <v>7036044</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5336,7 +5340,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5345,6 +5349,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5355,17 +5360,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5383,7 +5393,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131143967</v>
+        <v>131144264</v>
       </c>
       <c r="B38" t="n">
         <v>57892</v>
@@ -5416,7 +5426,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5426,10 +5436,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503201</v>
+        <v>503447</v>
       </c>
       <c r="R38" t="n">
-        <v>7036058</v>
+        <v>7035991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5466,7 +5476,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5483,11 +5493,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ38" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5498,14 +5503,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5523,10 +5523,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131143996</v>
+        <v>131143967</v>
       </c>
       <c r="B39" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5534,28 +5534,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5565,10 +5566,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503386</v>
+        <v>503201</v>
       </c>
       <c r="R39" t="n">
-        <v>7036016</v>
+        <v>7036058</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5605,7 +5606,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5614,7 +5615,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
+          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131144267</v>
+        <v>131144270</v>
       </c>
       <c r="B41" t="n">
-        <v>57892</v>
+        <v>80359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5795,31 +5795,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5827,10 +5822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503564</v>
+        <v>503423</v>
       </c>
       <c r="R41" t="n">
-        <v>7036045</v>
+        <v>7036145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5867,7 +5862,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5876,6 +5871,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5886,17 +5882,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5914,10 +5915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131144263</v>
+        <v>131144282</v>
       </c>
       <c r="B42" t="n">
-        <v>57892</v>
+        <v>80359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5925,31 +5926,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5957,10 +5953,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503363</v>
+        <v>503179</v>
       </c>
       <c r="R42" t="n">
-        <v>7035960</v>
+        <v>7035940</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5997,7 +5993,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6006,6 +6002,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6016,22 +6013,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6049,7 +6046,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131144270</v>
+        <v>131144276</v>
       </c>
       <c r="B43" t="n">
         <v>80359</v>
@@ -6087,10 +6084,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503423</v>
+        <v>503155</v>
       </c>
       <c r="R43" t="n">
-        <v>7036145</v>
+        <v>7035984</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6180,10 +6177,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131144282</v>
+        <v>131144267</v>
       </c>
       <c r="B44" t="n">
-        <v>80359</v>
+        <v>57892</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6191,26 +6188,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6218,10 +6220,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503179</v>
+        <v>503564</v>
       </c>
       <c r="R44" t="n">
-        <v>7035940</v>
+        <v>7036045</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6258,7 +6260,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6267,7 +6269,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6278,22 +6279,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6311,10 +6307,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131144276</v>
+        <v>131144263</v>
       </c>
       <c r="B45" t="n">
-        <v>80359</v>
+        <v>57892</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6322,26 +6318,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6349,10 +6350,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503155</v>
+        <v>503363</v>
       </c>
       <c r="R45" t="n">
-        <v>7035984</v>
+        <v>7035960</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6389,7 +6390,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6398,7 +6399,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6409,22 +6409,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -7717,10 +7717,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131143997</v>
+        <v>131144260</v>
       </c>
       <c r="B56" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7728,26 +7728,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7755,10 +7760,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503416</v>
+        <v>503332</v>
       </c>
       <c r="R56" t="n">
-        <v>7036029</v>
+        <v>7035948</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7793,13 +7798,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7818,9 +7827,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7838,10 +7852,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131143991</v>
+        <v>131144265</v>
       </c>
       <c r="B57" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7849,26 +7863,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7876,10 +7895,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503400</v>
+        <v>503516</v>
       </c>
       <c r="R57" t="n">
-        <v>7036159</v>
+        <v>7036022</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7914,13 +7933,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7959,7 +7982,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131143995</v>
+        <v>131143997</v>
       </c>
       <c r="B58" t="n">
         <v>79254</v>
@@ -7997,10 +8020,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503216</v>
+        <v>503416</v>
       </c>
       <c r="R58" t="n">
-        <v>7036078</v>
+        <v>7036029</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8080,10 +8103,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131143982</v>
+        <v>131143991</v>
       </c>
       <c r="B59" t="n">
-        <v>80359</v>
+        <v>79254</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8091,21 +8114,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8118,10 +8141,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503364</v>
+        <v>503400</v>
       </c>
       <c r="R59" t="n">
-        <v>7035989</v>
+        <v>7036159</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8173,22 +8196,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8206,10 +8224,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131144280</v>
+        <v>131143995</v>
       </c>
       <c r="B60" t="n">
-        <v>80359</v>
+        <v>79254</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8217,21 +8235,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8244,10 +8262,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503251</v>
+        <v>503216</v>
       </c>
       <c r="R60" t="n">
-        <v>7035966</v>
+        <v>7036078</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8282,11 +8300,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -8304,22 +8317,17 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8337,7 +8345,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131144275</v>
+        <v>131143982</v>
       </c>
       <c r="B61" t="n">
         <v>80359</v>
@@ -8375,10 +8383,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503195</v>
+        <v>503364</v>
       </c>
       <c r="R61" t="n">
-        <v>7036062</v>
+        <v>7035989</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8411,11 +8419,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8468,7 +8471,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131144291</v>
+        <v>131144280</v>
       </c>
       <c r="B62" t="n">
         <v>80359</v>
@@ -8506,10 +8509,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503317</v>
+        <v>503251</v>
       </c>
       <c r="R62" t="n">
-        <v>7035948</v>
+        <v>7035966</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8599,7 +8602,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131144297</v>
+        <v>131144275</v>
       </c>
       <c r="B63" t="n">
         <v>80359</v>
@@ -8637,10 +8640,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503354</v>
+        <v>503195</v>
       </c>
       <c r="R63" t="n">
-        <v>7036143</v>
+        <v>7036062</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8730,10 +8733,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131144260</v>
+        <v>131144291</v>
       </c>
       <c r="B64" t="n">
-        <v>57892</v>
+        <v>80359</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8741,31 +8744,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8773,7 +8771,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503332</v>
+        <v>503317</v>
       </c>
       <c r="R64" t="n">
         <v>7035948</v>
@@ -8813,7 +8811,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8822,6 +8820,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8832,22 +8831,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8865,10 +8864,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131144265</v>
+        <v>131144297</v>
       </c>
       <c r="B65" t="n">
-        <v>57892</v>
+        <v>80359</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8876,31 +8875,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8908,10 +8902,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503516</v>
+        <v>503354</v>
       </c>
       <c r="R65" t="n">
-        <v>7036022</v>
+        <v>7036143</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8948,7 +8942,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8957,6 +8951,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8967,17 +8962,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -10175,41 +10175,37 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131143970</v>
+        <v>131144302</v>
       </c>
       <c r="B75" t="n">
-        <v>80388</v>
+        <v>79254</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10217,10 +10213,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503376</v>
+        <v>503606</v>
       </c>
       <c r="R75" t="n">
-        <v>7035991</v>
+        <v>7036064</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10272,22 +10268,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10305,37 +10296,41 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131144273</v>
+        <v>131143970</v>
       </c>
       <c r="B76" t="n">
-        <v>80359</v>
+        <v>80388</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10343,10 +10338,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503267</v>
+        <v>503376</v>
       </c>
       <c r="R76" t="n">
-        <v>7036145</v>
+        <v>7035991</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10379,11 +10374,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10436,10 +10426,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131144302</v>
+        <v>131144273</v>
       </c>
       <c r="B77" t="n">
-        <v>79254</v>
+        <v>80359</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10447,21 +10437,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10474,10 +10464,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503606</v>
+        <v>503267</v>
       </c>
       <c r="R77" t="n">
-        <v>7036064</v>
+        <v>7036145</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10512,6 +10502,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10529,17 +10524,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>

--- a/artfynd/A 379-2026 artfynd.xlsx
+++ b/artfynd/A 379-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131144266</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131143977</v>
       </c>
       <c r="B3" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131143975</v>
       </c>
       <c r="B4" t="n">
-        <v>80388</v>
+        <v>80394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>131143973</v>
       </c>
       <c r="B5" t="n">
-        <v>80388</v>
+        <v>80394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131143999</v>
+        <v>131143978</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>80365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503460</v>
+        <v>503218</v>
       </c>
       <c r="R6" t="n">
-        <v>7036014</v>
+        <v>7036101</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,6 +1287,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1304,17 +1309,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1332,10 +1342,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131143978</v>
+        <v>131144271</v>
       </c>
       <c r="B7" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,10 +1380,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503218</v>
+        <v>503292</v>
       </c>
       <c r="R7" t="n">
-        <v>7036101</v>
+        <v>7036126</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1463,10 +1473,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131144271</v>
+        <v>131144288</v>
       </c>
       <c r="B8" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,10 +1511,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503292</v>
+        <v>503258</v>
       </c>
       <c r="R8" t="n">
-        <v>7036126</v>
+        <v>7035950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1594,10 +1604,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131144288</v>
+        <v>131144278</v>
       </c>
       <c r="B9" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,10 +1642,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503258</v>
+        <v>503277</v>
       </c>
       <c r="R9" t="n">
-        <v>7035950</v>
+        <v>7035964</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1725,10 +1735,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131144278</v>
+        <v>131143999</v>
       </c>
       <c r="B10" t="n">
-        <v>80359</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,21 +1746,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1763,10 +1773,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503277</v>
+        <v>503460</v>
       </c>
       <c r="R10" t="n">
-        <v>7035964</v>
+        <v>7036014</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1801,11 +1811,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1823,22 +1828,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1859,7 +1859,7 @@
         <v>131143990</v>
       </c>
       <c r="B11" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>131144287</v>
       </c>
       <c r="B12" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>131144272</v>
       </c>
       <c r="B13" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>131143987</v>
       </c>
       <c r="B14" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>131144279</v>
       </c>
       <c r="B15" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>131144296</v>
       </c>
       <c r="B16" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>131143980</v>
       </c>
       <c r="B17" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>131144292</v>
       </c>
       <c r="B18" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131143984</v>
       </c>
       <c r="B19" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>131144274</v>
       </c>
       <c r="B20" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>131143986</v>
       </c>
       <c r="B21" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3310,37 +3310,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131143998</v>
+        <v>131143972</v>
       </c>
       <c r="B22" t="n">
-        <v>79254</v>
+        <v>80394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3348,10 +3352,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503444</v>
+        <v>503377</v>
       </c>
       <c r="R22" t="n">
-        <v>7036006</v>
+        <v>7036016</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3388,7 +3392,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3408,17 +3412,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3436,41 +3445,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131143972</v>
+        <v>131143976</v>
       </c>
       <c r="B23" t="n">
-        <v>80388</v>
+        <v>80365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3478,10 +3483,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503377</v>
+        <v>503419</v>
       </c>
       <c r="R23" t="n">
-        <v>7036016</v>
+        <v>7036154</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3514,11 +3519,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131143976</v>
+        <v>131143989</v>
       </c>
       <c r="B24" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503419</v>
+        <v>503448</v>
       </c>
       <c r="R24" t="n">
-        <v>7036154</v>
+        <v>7036030</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3647,6 +3647,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Lunglav på en gran vid en rönn med lunglav.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3664,22 +3669,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3697,10 +3702,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131143989</v>
+        <v>131143998</v>
       </c>
       <c r="B25" t="n">
-        <v>80359</v>
+        <v>79260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3708,21 +3713,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3735,10 +3740,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503448</v>
+        <v>503444</v>
       </c>
       <c r="R25" t="n">
-        <v>7036030</v>
+        <v>7036006</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3775,7 +3780,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Lunglav på en gran vid en rönn med lunglav.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3803,14 +3808,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131144299</v>
+        <v>131144290</v>
       </c>
       <c r="B26" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503345</v>
+        <v>503313</v>
       </c>
       <c r="R26" t="n">
-        <v>7035956</v>
+        <v>7035948</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131144290</v>
+        <v>131143988</v>
       </c>
       <c r="B27" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503313</v>
+        <v>503421</v>
       </c>
       <c r="R27" t="n">
-        <v>7035948</v>
+        <v>7035997</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4033,11 +4033,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4090,10 +4085,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131144284</v>
+        <v>131144299</v>
       </c>
       <c r="B28" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4128,10 +4123,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503203</v>
+        <v>503345</v>
       </c>
       <c r="R28" t="n">
-        <v>7035913</v>
+        <v>7035956</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4221,10 +4216,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131143988</v>
+        <v>131144284</v>
       </c>
       <c r="B29" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4259,10 +4254,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503421</v>
+        <v>503203</v>
       </c>
       <c r="R29" t="n">
-        <v>7035997</v>
+        <v>7035913</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4295,6 +4290,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4347,10 +4347,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131143993</v>
+        <v>131144281</v>
       </c>
       <c r="B30" t="n">
-        <v>79254</v>
+        <v>80365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4358,21 +4358,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503307</v>
+        <v>503194</v>
       </c>
       <c r="R30" t="n">
-        <v>7036124</v>
+        <v>7035963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4445,17 +4445,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4473,10 +4478,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131143994</v>
+        <v>131144293</v>
       </c>
       <c r="B31" t="n">
-        <v>79254</v>
+        <v>80365</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4484,21 +4489,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4511,10 +4516,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503252</v>
+        <v>503484</v>
       </c>
       <c r="R31" t="n">
-        <v>7036082</v>
+        <v>7036019</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4551,7 +4556,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4571,17 +4576,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4599,10 +4609,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131144281</v>
+        <v>131143993</v>
       </c>
       <c r="B32" t="n">
-        <v>80359</v>
+        <v>79260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4610,21 +4620,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4637,10 +4647,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503194</v>
+        <v>503307</v>
       </c>
       <c r="R32" t="n">
-        <v>7035963</v>
+        <v>7036124</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4677,7 +4687,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4697,22 +4707,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4730,10 +4735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131144293</v>
+        <v>131143994</v>
       </c>
       <c r="B33" t="n">
-        <v>80359</v>
+        <v>79260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4741,21 +4746,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4768,10 +4773,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503484</v>
+        <v>503252</v>
       </c>
       <c r="R33" t="n">
-        <v>7036019</v>
+        <v>7036082</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4808,7 +4813,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4828,22 +4833,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131143996</v>
+        <v>131144269</v>
       </c>
       <c r="B34" t="n">
-        <v>79254</v>
+        <v>80366</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4872,30 +4872,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4903,10 +4899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503386</v>
+        <v>503190</v>
       </c>
       <c r="R34" t="n">
-        <v>7036016</v>
+        <v>7035938</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4943,7 +4939,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4961,29 +4957,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
-        </is>
-      </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5004,7 +4995,7 @@
         <v>131144259</v>
       </c>
       <c r="B35" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5131,10 +5122,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131144269</v>
+        <v>131144294</v>
       </c>
       <c r="B36" t="n">
-        <v>80360</v>
+        <v>80365</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5142,21 +5133,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5169,10 +5160,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503190</v>
+        <v>503563</v>
       </c>
       <c r="R36" t="n">
-        <v>7035938</v>
+        <v>7036044</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5262,10 +5253,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131144294</v>
+        <v>131144264</v>
       </c>
       <c r="B37" t="n">
-        <v>80359</v>
+        <v>57898</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5273,26 +5264,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5300,10 +5296,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503563</v>
+        <v>503447</v>
       </c>
       <c r="R37" t="n">
-        <v>7036044</v>
+        <v>7035991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5340,7 +5336,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5349,7 +5345,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5360,22 +5355,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5393,10 +5383,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131144264</v>
+        <v>131143967</v>
       </c>
       <c r="B38" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5426,7 +5416,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5436,10 +5426,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503447</v>
+        <v>503201</v>
       </c>
       <c r="R38" t="n">
-        <v>7035991</v>
+        <v>7036058</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5476,7 +5466,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5493,6 +5483,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ38" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5503,9 +5498,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5523,10 +5523,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131143967</v>
+        <v>131143996</v>
       </c>
       <c r="B39" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5534,29 +5534,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5566,10 +5565,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503201</v>
+        <v>503386</v>
       </c>
       <c r="R39" t="n">
-        <v>7036058</v>
+        <v>7036016</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5606,7 +5605,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
+          <t>Relativt rikligt med garnlav på flera granar. Långväxta bålar där vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5615,6 +5614,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Flerskiktad äldre granskog med stor stamdiameterspridning och ställvis gott om stående och liggande död ved.</t>
+          <t>Äldre flerskiktad granskog med stor stamdiameterspridning.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131143992</v>
+        <v>131144270</v>
       </c>
       <c r="B40" t="n">
-        <v>79254</v>
+        <v>80365</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5674,21 +5674,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503345</v>
+        <v>503423</v>
       </c>
       <c r="R40" t="n">
-        <v>7036137</v>
+        <v>7036145</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5739,6 +5739,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5756,17 +5761,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5784,10 +5794,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131144270</v>
+        <v>131144282</v>
       </c>
       <c r="B41" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5822,10 +5832,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503423</v>
+        <v>503179</v>
       </c>
       <c r="R41" t="n">
-        <v>7036145</v>
+        <v>7035940</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5915,10 +5925,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131144282</v>
+        <v>131144276</v>
       </c>
       <c r="B42" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5953,10 +5963,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503179</v>
+        <v>503155</v>
       </c>
       <c r="R42" t="n">
-        <v>7035940</v>
+        <v>7035984</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6046,10 +6056,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131144276</v>
+        <v>131143992</v>
       </c>
       <c r="B43" t="n">
-        <v>80359</v>
+        <v>79260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6057,21 +6067,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6084,10 +6094,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503155</v>
+        <v>503345</v>
       </c>
       <c r="R43" t="n">
-        <v>7035984</v>
+        <v>7036137</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6122,11 +6132,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6144,22 +6149,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6180,7 +6180,7 @@
         <v>131144267</v>
       </c>
       <c r="B44" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>131144263</v>
       </c>
       <c r="B45" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>131144295</v>
       </c>
       <c r="B46" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>131143981</v>
       </c>
       <c r="B47" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6699,10 +6699,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131144301</v>
+        <v>131144285</v>
       </c>
       <c r="B48" t="n">
-        <v>91842</v>
+        <v>80365</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6710,26 +6710,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503583</v>
+        <v>503209</v>
       </c>
       <c r="R48" t="n">
-        <v>7036073</v>
+        <v>7035903</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6775,6 +6775,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6792,17 +6797,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6820,10 +6830,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131144285</v>
+        <v>131143979</v>
       </c>
       <c r="B49" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6858,10 +6868,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503209</v>
+        <v>503343</v>
       </c>
       <c r="R49" t="n">
-        <v>7035903</v>
+        <v>7036013</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6894,11 +6904,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6951,10 +6956,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131143979</v>
+        <v>131144301</v>
       </c>
       <c r="B50" t="n">
-        <v>80359</v>
+        <v>91848</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6962,26 +6967,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6989,10 +6994,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503343</v>
+        <v>503583</v>
       </c>
       <c r="R50" t="n">
-        <v>7036013</v>
+        <v>7036073</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7044,22 +7049,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7077,32 +7077,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131143983</v>
+        <v>131144300</v>
       </c>
       <c r="B51" t="n">
-        <v>80359</v>
+        <v>80325</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503376</v>
+        <v>503318</v>
       </c>
       <c r="R51" t="n">
-        <v>7035991</v>
+        <v>7035950</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7151,6 +7151,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7203,32 +7208,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131144300</v>
+        <v>131143983</v>
       </c>
       <c r="B52" t="n">
-        <v>80319</v>
+        <v>80365</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7241,10 +7246,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503318</v>
+        <v>503376</v>
       </c>
       <c r="R52" t="n">
-        <v>7035950</v>
+        <v>7035991</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7277,11 +7282,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7337,7 +7337,7 @@
         <v>131144000</v>
       </c>
       <c r="B53" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>131144286</v>
       </c>
       <c r="B54" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>131144277</v>
       </c>
       <c r="B55" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7717,10 +7717,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131144260</v>
+        <v>131143997</v>
       </c>
       <c r="B56" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7728,31 +7728,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7760,10 +7755,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503332</v>
+        <v>503416</v>
       </c>
       <c r="R56" t="n">
-        <v>7035948</v>
+        <v>7036029</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7798,17 +7793,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7827,14 +7818,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7852,10 +7838,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131144265</v>
+        <v>131143991</v>
       </c>
       <c r="B57" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7863,31 +7849,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7895,10 +7876,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503516</v>
+        <v>503400</v>
       </c>
       <c r="R57" t="n">
-        <v>7036022</v>
+        <v>7036159</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7933,17 +7914,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7982,10 +7959,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131143997</v>
+        <v>131143995</v>
       </c>
       <c r="B58" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8020,10 +7997,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503416</v>
+        <v>503216</v>
       </c>
       <c r="R58" t="n">
-        <v>7036029</v>
+        <v>7036078</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8103,10 +8080,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131143991</v>
+        <v>131144260</v>
       </c>
       <c r="B59" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8114,26 +8091,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8141,10 +8123,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503400</v>
+        <v>503332</v>
       </c>
       <c r="R59" t="n">
-        <v>7036159</v>
+        <v>7035948</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8179,13 +8161,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8204,9 +8190,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8224,10 +8215,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131143995</v>
+        <v>131144265</v>
       </c>
       <c r="B60" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8235,26 +8226,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8262,10 +8258,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503216</v>
+        <v>503516</v>
       </c>
       <c r="R60" t="n">
-        <v>7036078</v>
+        <v>7036022</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8300,13 +8296,17 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -8348,7 +8348,7 @@
         <v>131143982</v>
       </c>
       <c r="B61" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>131144280</v>
       </c>
       <c r="B62" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>131144275</v>
       </c>
       <c r="B63" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>131144291</v>
       </c>
       <c r="B64" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>131144297</v>
       </c>
       <c r="B65" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8995,37 +8995,41 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131144001</v>
+        <v>131144268</v>
       </c>
       <c r="B66" t="n">
-        <v>79254</v>
+        <v>80394</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9033,10 +9037,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503574</v>
+        <v>503554</v>
       </c>
       <c r="R66" t="n">
-        <v>7036113</v>
+        <v>7036090</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9071,6 +9075,11 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9088,17 +9097,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9116,10 +9130,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131144268</v>
+        <v>131143968</v>
       </c>
       <c r="B67" t="n">
-        <v>80388</v>
+        <v>80394</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9158,10 +9172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503554</v>
+        <v>503216</v>
       </c>
       <c r="R67" t="n">
-        <v>7036090</v>
+        <v>7036102</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9251,41 +9265,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131143968</v>
+        <v>131144283</v>
       </c>
       <c r="B68" t="n">
-        <v>80388</v>
+        <v>80365</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9293,10 +9303,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503216</v>
+        <v>503196</v>
       </c>
       <c r="R68" t="n">
-        <v>7036102</v>
+        <v>7035909</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9386,32 +9396,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131144283</v>
+        <v>131143974</v>
       </c>
       <c r="B69" t="n">
-        <v>80359</v>
+        <v>80394</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9424,10 +9434,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503196</v>
+        <v>503424</v>
       </c>
       <c r="R69" t="n">
-        <v>7035909</v>
+        <v>7036001</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9517,32 +9527,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131143974</v>
+        <v>131144298</v>
       </c>
       <c r="B70" t="n">
-        <v>80388</v>
+        <v>80365</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9555,10 +9565,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503424</v>
+        <v>503191</v>
       </c>
       <c r="R70" t="n">
-        <v>7036001</v>
+        <v>7035913</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9648,10 +9658,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131144298</v>
+        <v>131144001</v>
       </c>
       <c r="B71" t="n">
-        <v>80359</v>
+        <v>79260</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9659,21 +9669,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9686,10 +9696,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503191</v>
+        <v>503574</v>
       </c>
       <c r="R71" t="n">
-        <v>7035913</v>
+        <v>7036113</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9724,11 +9734,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9746,22 +9751,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
         <v>131144262</v>
       </c>
       <c r="B72" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9909,10 +9909,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131144289</v>
+        <v>131144261</v>
       </c>
       <c r="B73" t="n">
-        <v>80359</v>
+        <v>57898</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9920,26 +9920,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9947,10 +9952,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503258</v>
+        <v>503332</v>
       </c>
       <c r="R73" t="n">
-        <v>7035952</v>
+        <v>7035950</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9987,7 +9992,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9996,7 +10001,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -10007,22 +10011,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10040,10 +10044,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131144261</v>
+        <v>131144289</v>
       </c>
       <c r="B74" t="n">
-        <v>57892</v>
+        <v>80365</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10051,31 +10055,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10083,10 +10082,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503332</v>
+        <v>503258</v>
       </c>
       <c r="R74" t="n">
-        <v>7035950</v>
+        <v>7035952</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10123,7 +10122,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10132,6 +10131,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10175,37 +10175,41 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131144302</v>
+        <v>131143970</v>
       </c>
       <c r="B75" t="n">
-        <v>79254</v>
+        <v>80394</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10213,10 +10217,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503606</v>
+        <v>503376</v>
       </c>
       <c r="R75" t="n">
-        <v>7036064</v>
+        <v>7035991</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10268,17 +10272,22 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10296,41 +10305,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131143970</v>
+        <v>131144273</v>
       </c>
       <c r="B76" t="n">
-        <v>80388</v>
+        <v>80365</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10338,10 +10343,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503376</v>
+        <v>503267</v>
       </c>
       <c r="R76" t="n">
-        <v>7035991</v>
+        <v>7036145</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10374,6 +10379,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10426,10 +10436,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131144273</v>
+        <v>131144302</v>
       </c>
       <c r="B77" t="n">
-        <v>80359</v>
+        <v>79260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10437,21 +10447,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10464,10 +10474,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503267</v>
+        <v>503606</v>
       </c>
       <c r="R77" t="n">
-        <v>7036145</v>
+        <v>7036064</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10502,11 +10512,6 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10524,22 +10529,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
